--- a/data/raw/PETR4.SA.xlsx
+++ b/data/raw/PETR4.SA.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F252"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,5022 +468,5002 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>45833</v>
+        <v>45845</v>
       </c>
       <c r="B2" t="n">
-        <v>28.68923187255859</v>
+        <v>29.4705810546875</v>
       </c>
       <c r="C2" t="n">
-        <v>28.99258013680789</v>
+        <v>29.65442466109395</v>
       </c>
       <c r="D2" t="n">
-        <v>28.68923187255859</v>
+        <v>29.32350231231112</v>
       </c>
       <c r="E2" t="n">
-        <v>28.79034796064169</v>
+        <v>29.52573273397262</v>
       </c>
       <c r="F2" t="n">
-        <v>23127700</v>
+        <v>17938800</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>45834</v>
+        <v>45846</v>
       </c>
       <c r="B3" t="n">
-        <v>28.91904067993164</v>
+        <v>29.89342880249023</v>
       </c>
       <c r="C3" t="n">
-        <v>29.04773436463997</v>
+        <v>29.95777477001694</v>
       </c>
       <c r="D3" t="n">
-        <v>28.78115621723335</v>
+        <v>29.44300352321104</v>
       </c>
       <c r="E3" t="n">
-        <v>28.81792634237746</v>
+        <v>29.47977364939551</v>
       </c>
       <c r="F3" t="n">
-        <v>17227000</v>
+        <v>28778300</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>45835</v>
+        <v>45847</v>
       </c>
       <c r="B4" t="n">
-        <v>28.68923187255859</v>
+        <v>29.70957946777344</v>
       </c>
       <c r="C4" t="n">
-        <v>28.90984911079372</v>
+        <v>29.99454266461354</v>
       </c>
       <c r="D4" t="n">
-        <v>28.62488590861336</v>
+        <v>29.4705806785403</v>
       </c>
       <c r="E4" t="n">
-        <v>28.85469392458693</v>
+        <v>29.93938747944037</v>
       </c>
       <c r="F4" t="n">
-        <v>16482100</v>
+        <v>22338900</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>45838</v>
+        <v>45848</v>
       </c>
       <c r="B5" t="n">
-        <v>28.84550285339355</v>
+        <v>29.63604354858398</v>
       </c>
       <c r="C5" t="n">
-        <v>28.94661894659403</v>
+        <v>29.81069637991679</v>
       </c>
       <c r="D5" t="n">
-        <v>28.58811898458667</v>
+        <v>29.15804069698587</v>
       </c>
       <c r="E5" t="n">
-        <v>28.68923332449105</v>
+        <v>29.42461708619155</v>
       </c>
       <c r="F5" t="n">
-        <v>23091100</v>
+        <v>23102800</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>45839</v>
+        <v>45849</v>
       </c>
       <c r="B6" t="n">
-        <v>28.94661712646484</v>
+        <v>29.99454498291016</v>
       </c>
       <c r="C6" t="n">
-        <v>29.02015562054224</v>
+        <v>30.05889095062288</v>
       </c>
       <c r="D6" t="n">
-        <v>28.73519417515433</v>
+        <v>29.55331398719768</v>
       </c>
       <c r="E6" t="n">
-        <v>28.90984875607415</v>
+        <v>29.59927489176501</v>
       </c>
       <c r="F6" t="n">
-        <v>17014100</v>
+        <v>23946700</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>45840</v>
+        <v>45852</v>
       </c>
       <c r="B7" t="n">
-        <v>29.46138763427734</v>
+        <v>29.59927177429199</v>
       </c>
       <c r="C7" t="n">
-        <v>29.63604397471356</v>
+        <v>30.12323374567753</v>
       </c>
       <c r="D7" t="n">
-        <v>28.93742562615293</v>
+        <v>29.52573152945591</v>
       </c>
       <c r="E7" t="n">
-        <v>29.02934918534755</v>
+        <v>29.99454182380626</v>
       </c>
       <c r="F7" t="n">
-        <v>28311600</v>
+        <v>24106300</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>45841</v>
+        <v>45853</v>
       </c>
       <c r="B8" t="n">
-        <v>29.56250381469727</v>
+        <v>29.36946678161621</v>
       </c>
       <c r="C8" t="n">
-        <v>29.77392677418112</v>
+        <v>29.76473687167498</v>
       </c>
       <c r="D8" t="n">
-        <v>29.36027338649046</v>
+        <v>29.24077309324835</v>
       </c>
       <c r="E8" t="n">
-        <v>29.41542682085667</v>
+        <v>29.63604493660324</v>
       </c>
       <c r="F8" t="n">
-        <v>14322300</v>
+        <v>18688300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>45842</v>
+        <v>45854</v>
       </c>
       <c r="B9" t="n">
-        <v>29.52573394775391</v>
+        <v>29.22239112854004</v>
       </c>
       <c r="C9" t="n">
-        <v>29.70039029024885</v>
+        <v>29.36946813347651</v>
       </c>
       <c r="D9" t="n">
-        <v>29.38784948398473</v>
+        <v>28.9282353653709</v>
       </c>
       <c r="E9" t="n">
-        <v>29.415427078057</v>
+        <v>29.32350547362374</v>
       </c>
       <c r="F9" t="n">
-        <v>9356900</v>
+        <v>27588900</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45845</v>
+        <v>45855</v>
       </c>
       <c r="B10" t="n">
-        <v>29.47058296203613</v>
+        <v>28.9282341003418</v>
       </c>
       <c r="C10" t="n">
-        <v>29.65442658034102</v>
+        <v>29.2040047875104</v>
       </c>
       <c r="D10" t="n">
-        <v>29.32350421014075</v>
+        <v>28.86388813265796</v>
       </c>
       <c r="E10" t="n">
-        <v>29.5257346448907</v>
+        <v>29.2040047875104</v>
       </c>
       <c r="F10" t="n">
-        <v>17938800</v>
+        <v>27497600</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45846</v>
+        <v>45856</v>
       </c>
       <c r="B11" t="n">
-        <v>29.89342880249023</v>
+        <v>28.48700332641602</v>
       </c>
       <c r="C11" t="n">
-        <v>29.95777477001694</v>
+        <v>29.04773548338737</v>
       </c>
       <c r="D11" t="n">
-        <v>29.44300352321104</v>
+        <v>28.12850335893394</v>
       </c>
       <c r="E11" t="n">
-        <v>29.47977364939551</v>
+        <v>28.86388835717823</v>
       </c>
       <c r="F11" t="n">
-        <v>28778300</v>
+        <v>57635000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45847</v>
+        <v>45859</v>
       </c>
       <c r="B12" t="n">
-        <v>29.70957946777344</v>
+        <v>28.54215431213379</v>
       </c>
       <c r="C12" t="n">
-        <v>29.99454266461354</v>
+        <v>28.75357901510876</v>
       </c>
       <c r="D12" t="n">
-        <v>29.4705806785403</v>
+        <v>28.28477046149711</v>
       </c>
       <c r="E12" t="n">
-        <v>29.93938747944037</v>
+        <v>28.39507732511398</v>
       </c>
       <c r="F12" t="n">
-        <v>22338900</v>
+        <v>16412000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45848</v>
+        <v>45860</v>
       </c>
       <c r="B13" t="n">
-        <v>29.63604545593262</v>
+        <v>28.81792640686035</v>
       </c>
       <c r="C13" t="n">
-        <v>29.81069829850592</v>
+        <v>29.02934936702388</v>
       </c>
       <c r="D13" t="n">
-        <v>29.15804257357068</v>
+        <v>28.48700229300713</v>
       </c>
       <c r="E13" t="n">
-        <v>29.42461897993297</v>
+        <v>28.54215572755064</v>
       </c>
       <c r="F13" t="n">
-        <v>23102800</v>
+        <v>24557100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45849</v>
+        <v>45861</v>
       </c>
       <c r="B14" t="n">
-        <v>29.99454689025879</v>
+        <v>29.4062328338623</v>
       </c>
       <c r="C14" t="n">
-        <v>30.05889286206326</v>
+        <v>29.44300120385425</v>
       </c>
       <c r="D14" t="n">
-        <v>29.55331586648849</v>
+        <v>28.77196223351342</v>
       </c>
       <c r="E14" t="n">
-        <v>29.59927677397848</v>
+        <v>28.81792488762333</v>
       </c>
       <c r="F14" t="n">
-        <v>23946700</v>
+        <v>27418600</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45852</v>
+        <v>45862</v>
       </c>
       <c r="B15" t="n">
-        <v>29.59927368164062</v>
+        <v>29.36027336120605</v>
       </c>
       <c r="C15" t="n">
-        <v>30.12323568678977</v>
+        <v>29.43381185806302</v>
       </c>
       <c r="D15" t="n">
-        <v>29.52573343206568</v>
+        <v>29.0936952142895</v>
       </c>
       <c r="E15" t="n">
-        <v>29.99454375662571</v>
+        <v>29.35108082993693</v>
       </c>
       <c r="F15" t="n">
-        <v>24106300</v>
+        <v>17856300</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45853</v>
+        <v>45863</v>
       </c>
       <c r="B16" t="n">
-        <v>29.36946678161621</v>
+        <v>29.39704132080078</v>
       </c>
       <c r="C16" t="n">
-        <v>29.76473687167498</v>
+        <v>29.58088843701346</v>
       </c>
       <c r="D16" t="n">
-        <v>29.24077309324835</v>
+        <v>29.33269535611516</v>
       </c>
       <c r="E16" t="n">
-        <v>29.63604493660324</v>
+        <v>29.40623385194102</v>
       </c>
       <c r="F16" t="n">
-        <v>18688300</v>
+        <v>13341000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45854</v>
+        <v>45866</v>
       </c>
       <c r="B17" t="n">
-        <v>29.22238922119141</v>
+        <v>29.43381118774414</v>
       </c>
       <c r="C17" t="n">
-        <v>29.36946621652814</v>
+        <v>29.81069619471502</v>
       </c>
       <c r="D17" t="n">
-        <v>28.92823347722185</v>
+        <v>29.12127214489569</v>
       </c>
       <c r="E17" t="n">
-        <v>29.32350355967536</v>
+        <v>29.56250311598902</v>
       </c>
       <c r="F17" t="n">
-        <v>27588900</v>
+        <v>27972800</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45855</v>
+        <v>45867</v>
       </c>
       <c r="B18" t="n">
-        <v>28.92823219299316</v>
+        <v>29.81988716125488</v>
       </c>
       <c r="C18" t="n">
-        <v>29.20400286197916</v>
+        <v>29.9669641525504</v>
       </c>
       <c r="D18" t="n">
-        <v>28.8638862295519</v>
+        <v>29.40623378072225</v>
       </c>
       <c r="E18" t="n">
-        <v>29.20400286197916</v>
+        <v>29.59007914319363</v>
       </c>
       <c r="F18" t="n">
-        <v>27497600</v>
+        <v>33284000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45856</v>
+        <v>45868</v>
       </c>
       <c r="B19" t="n">
-        <v>28.48700332641602</v>
+        <v>30.12323379516602</v>
       </c>
       <c r="C19" t="n">
-        <v>29.04773548338737</v>
+        <v>30.17838897888369</v>
       </c>
       <c r="D19" t="n">
-        <v>28.12850335893394</v>
+        <v>29.66361778396103</v>
       </c>
       <c r="E19" t="n">
-        <v>28.86388835717823</v>
+        <v>29.69119362252393</v>
       </c>
       <c r="F19" t="n">
-        <v>57635000</v>
+        <v>27110400</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45859</v>
+        <v>45869</v>
       </c>
       <c r="B20" t="n">
-        <v>28.54215431213379</v>
+        <v>30.00373458862305</v>
       </c>
       <c r="C20" t="n">
-        <v>28.75357901510876</v>
+        <v>30.10485067867486</v>
       </c>
       <c r="D20" t="n">
-        <v>28.28477046149711</v>
+        <v>29.80150240851942</v>
       </c>
       <c r="E20" t="n">
-        <v>28.39507732511398</v>
+        <v>29.8290817554558</v>
       </c>
       <c r="F20" t="n">
-        <v>16412000</v>
+        <v>23544900</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>45860</v>
+        <v>45870</v>
       </c>
       <c r="B21" t="n">
-        <v>28.81792640686035</v>
+        <v>29.60846328735352</v>
       </c>
       <c r="C21" t="n">
-        <v>29.02934936702388</v>
+        <v>30.25192641929143</v>
       </c>
       <c r="D21" t="n">
-        <v>28.48700229300713</v>
+        <v>29.45219552308149</v>
       </c>
       <c r="E21" t="n">
-        <v>28.54215572755064</v>
+        <v>30.15081033342508</v>
       </c>
       <c r="F21" t="n">
-        <v>24557100</v>
+        <v>24191800</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45861</v>
+        <v>45873</v>
       </c>
       <c r="B22" t="n">
-        <v>29.40623474121094</v>
+        <v>29.56250381469727</v>
       </c>
       <c r="C22" t="n">
-        <v>29.44300311358776</v>
+        <v>29.6636199054487</v>
       </c>
       <c r="D22" t="n">
-        <v>28.77196409972197</v>
+        <v>29.37865669574848</v>
       </c>
       <c r="E22" t="n">
-        <v>28.8179267568131</v>
+        <v>29.60846471778643</v>
       </c>
       <c r="F22" t="n">
-        <v>27418600</v>
+        <v>15215600</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45862</v>
+        <v>45874</v>
       </c>
       <c r="B23" t="n">
-        <v>29.36027336120605</v>
+        <v>29.70038986206055</v>
       </c>
       <c r="C23" t="n">
-        <v>29.43381185806302</v>
+        <v>29.79231166771738</v>
       </c>
       <c r="D23" t="n">
-        <v>29.0936952142895</v>
+        <v>29.44300249435561</v>
       </c>
       <c r="E23" t="n">
-        <v>29.35108082993693</v>
+        <v>29.53492780660456</v>
       </c>
       <c r="F23" t="n">
-        <v>17856300</v>
+        <v>20635500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45863</v>
+        <v>45875</v>
       </c>
       <c r="B24" t="n">
-        <v>29.39704132080078</v>
+        <v>29.73715400695801</v>
       </c>
       <c r="C24" t="n">
-        <v>29.58088843701346</v>
+        <v>30.27950103104427</v>
       </c>
       <c r="D24" t="n">
-        <v>29.33269535611516</v>
+        <v>29.59007702618505</v>
       </c>
       <c r="E24" t="n">
-        <v>29.40623385194102</v>
+        <v>29.96696200857775</v>
       </c>
       <c r="F24" t="n">
-        <v>13341000</v>
+        <v>32854600</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45866</v>
+        <v>45876</v>
       </c>
       <c r="B25" t="n">
-        <v>29.43381118774414</v>
+        <v>29.90261650085449</v>
       </c>
       <c r="C25" t="n">
-        <v>29.81069619471502</v>
+        <v>30.19677046684876</v>
       </c>
       <c r="D25" t="n">
-        <v>29.12127214489569</v>
+        <v>29.81069470145323</v>
       </c>
       <c r="E25" t="n">
-        <v>29.56250311598902</v>
+        <v>30.003732584151</v>
       </c>
       <c r="F25" t="n">
-        <v>27972800</v>
+        <v>21111400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45867</v>
+        <v>45877</v>
       </c>
       <c r="B26" t="n">
-        <v>29.81988906860352</v>
+        <v>28.06415748596191</v>
       </c>
       <c r="C26" t="n">
-        <v>29.96696606930642</v>
+        <v>29.46138898736639</v>
       </c>
       <c r="D26" t="n">
-        <v>29.40623566161266</v>
+        <v>28.06415748596191</v>
       </c>
       <c r="E26" t="n">
-        <v>29.59008103584321</v>
+        <v>28.95581201852021</v>
       </c>
       <c r="F26" t="n">
-        <v>33284000</v>
+        <v>107235300</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45868</v>
+        <v>45880</v>
       </c>
       <c r="B27" t="n">
-        <v>30.12323570251465</v>
+        <v>28.23880767822266</v>
       </c>
       <c r="C27" t="n">
-        <v>30.17839088972465</v>
+        <v>28.52377087340555</v>
       </c>
       <c r="D27" t="n">
-        <v>29.6636196622076</v>
+        <v>28.1101157534923</v>
       </c>
       <c r="E27" t="n">
-        <v>29.69119550251655</v>
+        <v>28.22961514741392</v>
       </c>
       <c r="F27" t="n">
-        <v>27110400</v>
+        <v>28045800</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45869</v>
+        <v>45881</v>
       </c>
       <c r="B28" t="n">
-        <v>30.00373458862305</v>
+        <v>28.31234741210938</v>
       </c>
       <c r="C28" t="n">
-        <v>30.10485067867486</v>
+        <v>28.74438761257311</v>
       </c>
       <c r="D28" t="n">
-        <v>29.80150240851942</v>
+        <v>28.17446295052787</v>
       </c>
       <c r="E28" t="n">
-        <v>29.8290817554558</v>
+        <v>28.30315663419385</v>
       </c>
       <c r="F28" t="n">
-        <v>23544900</v>
+        <v>37973300</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45870</v>
+        <v>45882</v>
       </c>
       <c r="B29" t="n">
-        <v>29.60846519470215</v>
+        <v>28.10092544555664</v>
       </c>
       <c r="C29" t="n">
-        <v>30.25192836809134</v>
+        <v>28.36750360020925</v>
       </c>
       <c r="D29" t="n">
-        <v>29.4521974203635</v>
+        <v>27.95384844757455</v>
       </c>
       <c r="E29" t="n">
-        <v>30.15081227571119</v>
+        <v>28.31234841099388</v>
       </c>
       <c r="F29" t="n">
-        <v>24191800</v>
+        <v>38340700</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45873</v>
+        <v>45883</v>
       </c>
       <c r="B30" t="n">
-        <v>29.56250381469727</v>
+        <v>27.74242401123047</v>
       </c>
       <c r="C30" t="n">
-        <v>29.6636199054487</v>
+        <v>28.24800094582613</v>
       </c>
       <c r="D30" t="n">
-        <v>29.37865669574848</v>
+        <v>27.59534702104642</v>
       </c>
       <c r="E30" t="n">
-        <v>29.60846471778643</v>
+        <v>28.24800094582613</v>
       </c>
       <c r="F30" t="n">
-        <v>15215600</v>
+        <v>43087500</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45874</v>
+        <v>45884</v>
       </c>
       <c r="B31" t="n">
-        <v>29.70038986206055</v>
+        <v>27.73323249816895</v>
       </c>
       <c r="C31" t="n">
-        <v>29.79231166771738</v>
+        <v>27.77919340180251</v>
       </c>
       <c r="D31" t="n">
-        <v>29.44300249435561</v>
+        <v>27.33796241505437</v>
       </c>
       <c r="E31" t="n">
-        <v>29.53492780660456</v>
+        <v>27.66888653176352</v>
       </c>
       <c r="F31" t="n">
-        <v>20635500</v>
+        <v>55416100</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45875</v>
+        <v>45887</v>
       </c>
       <c r="B32" t="n">
-        <v>29.73715591430664</v>
+        <v>27.90788650512695</v>
       </c>
       <c r="C32" t="n">
-        <v>30.27950297317918</v>
+        <v>28.08253933792421</v>
       </c>
       <c r="D32" t="n">
-        <v>29.59007892410012</v>
+        <v>27.59534745771622</v>
       </c>
       <c r="E32" t="n">
-        <v>29.96696393066633</v>
+        <v>27.80677041528935</v>
       </c>
       <c r="F32" t="n">
-        <v>32854600</v>
+        <v>31498100</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45876</v>
+        <v>45888</v>
       </c>
       <c r="B33" t="n">
-        <v>29.90261840820312</v>
+        <v>27.61373138427734</v>
       </c>
       <c r="C33" t="n">
-        <v>30.19677239296011</v>
+        <v>27.78838420989066</v>
       </c>
       <c r="D33" t="n">
-        <v>29.81069660293861</v>
+        <v>27.43907680536805</v>
       </c>
       <c r="E33" t="n">
-        <v>30.00373449794936</v>
+        <v>27.76080837073907</v>
       </c>
       <c r="F33" t="n">
-        <v>21111400</v>
+        <v>39294300</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45877</v>
+        <v>45889</v>
       </c>
       <c r="B34" t="n">
-        <v>28.06415748596191</v>
+        <v>27.77919387817383</v>
       </c>
       <c r="C34" t="n">
-        <v>29.46138898736639</v>
+        <v>27.90788756648767</v>
       </c>
       <c r="D34" t="n">
-        <v>28.06415748596191</v>
+        <v>27.66888700624324</v>
       </c>
       <c r="E34" t="n">
-        <v>28.95581201852021</v>
+        <v>27.68727206933038</v>
       </c>
       <c r="F34" t="n">
-        <v>107235300</v>
+        <v>23706600</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45880</v>
+        <v>45890</v>
       </c>
       <c r="B35" t="n">
-        <v>28.23880958557129</v>
+        <v>27.84354019165039</v>
       </c>
       <c r="C35" t="n">
-        <v>28.52377280000161</v>
+        <v>27.97223212016349</v>
       </c>
       <c r="D35" t="n">
-        <v>28.11011765214863</v>
+        <v>27.58615458132816</v>
       </c>
       <c r="E35" t="n">
-        <v>28.22961705414166</v>
+        <v>27.77919247409781</v>
       </c>
       <c r="F35" t="n">
-        <v>28045800</v>
+        <v>23327000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45881</v>
+        <v>45891</v>
       </c>
       <c r="B36" t="n">
-        <v>28.31234931945801</v>
+        <v>28.64441871643066</v>
       </c>
       <c r="C36" t="n">
-        <v>28.74438954902746</v>
+        <v>28.64441871643066</v>
       </c>
       <c r="D36" t="n">
-        <v>28.17446484858749</v>
+        <v>28.01456104797339</v>
       </c>
       <c r="E36" t="n">
-        <v>28.30315854092332</v>
+        <v>28.09916892829389</v>
       </c>
       <c r="F36" t="n">
-        <v>37973300</v>
+        <v>49813600</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45882</v>
+        <v>45894</v>
       </c>
       <c r="B37" t="n">
-        <v>28.10092353820801</v>
+        <v>28.81363677978516</v>
       </c>
       <c r="C37" t="n">
-        <v>28.36750167476664</v>
+        <v>28.93584896915797</v>
       </c>
       <c r="D37" t="n">
-        <v>27.95384655020876</v>
+        <v>28.59741742082935</v>
       </c>
       <c r="E37" t="n">
-        <v>28.31234648929492</v>
+        <v>28.64442100562085</v>
       </c>
       <c r="F37" t="n">
-        <v>38340700</v>
+        <v>21075300</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45883</v>
+        <v>45895</v>
       </c>
       <c r="B38" t="n">
-        <v>27.74242401123047</v>
+        <v>28.6068172454834</v>
       </c>
       <c r="C38" t="n">
-        <v>28.24800094582613</v>
+        <v>28.74782978676352</v>
       </c>
       <c r="D38" t="n">
-        <v>27.59534702104642</v>
+        <v>28.41879932839541</v>
       </c>
       <c r="E38" t="n">
-        <v>28.24800094582613</v>
+        <v>28.65382082821952</v>
       </c>
       <c r="F38" t="n">
-        <v>43087500</v>
+        <v>21789700</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45884</v>
+        <v>45896</v>
       </c>
       <c r="B39" t="n">
-        <v>27.73323249816895</v>
+        <v>28.82303810119629</v>
       </c>
       <c r="C39" t="n">
-        <v>27.77919340180251</v>
+        <v>28.84184025250199</v>
       </c>
       <c r="D39" t="n">
-        <v>27.33796241505437</v>
+        <v>28.54101300389819</v>
       </c>
       <c r="E39" t="n">
-        <v>27.66888653176352</v>
+        <v>28.62562089170199</v>
       </c>
       <c r="F39" t="n">
-        <v>55416100</v>
+        <v>16349100</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45887</v>
+        <v>45897</v>
       </c>
       <c r="B40" t="n">
-        <v>27.90788841247559</v>
+        <v>29.07686233520508</v>
       </c>
       <c r="C40" t="n">
-        <v>28.08254125720939</v>
+        <v>29.26487847273611</v>
       </c>
       <c r="D40" t="n">
-        <v>27.59534934370454</v>
+        <v>28.8700422529275</v>
       </c>
       <c r="E40" t="n">
-        <v>27.80677231572726</v>
+        <v>28.93584978378884</v>
       </c>
       <c r="F40" t="n">
-        <v>31498100</v>
+        <v>25802500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45888</v>
+        <v>45898</v>
       </c>
       <c r="B41" t="n">
-        <v>27.61373138427734</v>
+        <v>29.2366771697998</v>
       </c>
       <c r="C41" t="n">
-        <v>27.78838420989066</v>
+        <v>29.47169868757461</v>
       </c>
       <c r="D41" t="n">
-        <v>27.43907680536805</v>
+        <v>29.001655652025</v>
       </c>
       <c r="E41" t="n">
-        <v>27.76080837073907</v>
+        <v>29.07686246599006</v>
       </c>
       <c r="F41" t="n">
-        <v>39294300</v>
+        <v>27713400</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45889</v>
+        <v>45901</v>
       </c>
       <c r="B42" t="n">
-        <v>27.77919578552246</v>
+        <v>29.30248069763184</v>
       </c>
       <c r="C42" t="n">
-        <v>27.90788948267255</v>
+        <v>29.49049861489845</v>
       </c>
       <c r="D42" t="n">
-        <v>27.66888890601809</v>
+        <v>29.18966958865752</v>
       </c>
       <c r="E42" t="n">
-        <v>27.68727397036756</v>
+        <v>29.33068392314335</v>
       </c>
       <c r="F42" t="n">
-        <v>23706600</v>
+        <v>9889700</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45890</v>
+        <v>45902</v>
       </c>
       <c r="B43" t="n">
-        <v>27.84354019165039</v>
+        <v>29.45289421081543</v>
       </c>
       <c r="C43" t="n">
-        <v>27.97223212016349</v>
+        <v>29.5563042442562</v>
       </c>
       <c r="D43" t="n">
-        <v>27.58615458132816</v>
+        <v>29.14266590356487</v>
       </c>
       <c r="E43" t="n">
-        <v>27.77919247409781</v>
+        <v>29.14266590356487</v>
       </c>
       <c r="F43" t="n">
-        <v>23327000</v>
+        <v>19812000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45891</v>
+        <v>45903</v>
       </c>
       <c r="B44" t="n">
-        <v>28.64441871643066</v>
+        <v>29.19906997680664</v>
       </c>
       <c r="C44" t="n">
-        <v>28.64441871643066</v>
+        <v>29.47169577112148</v>
       </c>
       <c r="D44" t="n">
-        <v>28.01456104797339</v>
+        <v>29.06745851365973</v>
       </c>
       <c r="E44" t="n">
-        <v>28.09916892829389</v>
+        <v>29.25547642650249</v>
       </c>
       <c r="F44" t="n">
-        <v>49813600</v>
+        <v>29788800</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45894</v>
+        <v>45904</v>
       </c>
       <c r="B45" t="n">
-        <v>28.81363677978516</v>
+        <v>29.19906997680664</v>
       </c>
       <c r="C45" t="n">
-        <v>28.93584896915797</v>
+        <v>29.44349254627355</v>
       </c>
       <c r="D45" t="n">
-        <v>28.59741742082935</v>
+        <v>29.07685958860904</v>
       </c>
       <c r="E45" t="n">
-        <v>28.64442100562085</v>
+        <v>29.14266532018249</v>
       </c>
       <c r="F45" t="n">
-        <v>21075300</v>
+        <v>24816500</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45895</v>
+        <v>45905</v>
       </c>
       <c r="B46" t="n">
-        <v>28.60681915283203</v>
+        <v>28.75723075866699</v>
       </c>
       <c r="C46" t="n">
-        <v>28.74783170351411</v>
+        <v>29.22727375662746</v>
       </c>
       <c r="D46" t="n">
-        <v>28.41880122320801</v>
+        <v>28.38119671891297</v>
       </c>
       <c r="E46" t="n">
-        <v>28.6538227387021</v>
+        <v>29.21787268149964</v>
       </c>
       <c r="F46" t="n">
-        <v>21789700</v>
+        <v>46121900</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>45896</v>
+        <v>45908</v>
       </c>
       <c r="B47" t="n">
-        <v>28.82303810119629</v>
+        <v>28.87004089355469</v>
       </c>
       <c r="C47" t="n">
-        <v>28.84184025250199</v>
+        <v>29.11446347460085</v>
       </c>
       <c r="D47" t="n">
-        <v>28.54101300389819</v>
+        <v>28.68202476487657</v>
       </c>
       <c r="E47" t="n">
-        <v>28.62562089170199</v>
+        <v>28.98285200521899</v>
       </c>
       <c r="F47" t="n">
-        <v>16349100</v>
+        <v>18164200</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>45897</v>
+        <v>45909</v>
       </c>
       <c r="B48" t="n">
-        <v>29.07686233520508</v>
+        <v>29.09566307067871</v>
       </c>
       <c r="C48" t="n">
-        <v>29.26487847273611</v>
+        <v>29.28367919905826</v>
       </c>
       <c r="D48" t="n">
-        <v>28.8700422529275</v>
+        <v>28.96404980843406</v>
       </c>
       <c r="E48" t="n">
-        <v>28.93584978378884</v>
+        <v>29.01105518533279</v>
       </c>
       <c r="F48" t="n">
-        <v>25802500</v>
+        <v>31283900</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>45898</v>
+        <v>45910</v>
       </c>
       <c r="B49" t="n">
-        <v>29.2366771697998</v>
+        <v>29.62211036682129</v>
       </c>
       <c r="C49" t="n">
-        <v>29.47169868757461</v>
+        <v>29.6503135926048</v>
       </c>
       <c r="D49" t="n">
-        <v>29.001655652025</v>
+        <v>29.06745947791458</v>
       </c>
       <c r="E49" t="n">
-        <v>29.07686246599006</v>
+        <v>29.1050619858875</v>
       </c>
       <c r="F49" t="n">
-        <v>27713400</v>
+        <v>35949600</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>45901</v>
+        <v>45911</v>
       </c>
       <c r="B50" t="n">
-        <v>29.30248069763184</v>
+        <v>29.50930023193359</v>
       </c>
       <c r="C50" t="n">
-        <v>29.49049861489845</v>
+        <v>29.59390811900834</v>
       </c>
       <c r="D50" t="n">
-        <v>29.18966958865752</v>
+        <v>29.39649091121514</v>
       </c>
       <c r="E50" t="n">
-        <v>29.33068392314335</v>
+        <v>29.42469234485884</v>
       </c>
       <c r="F50" t="n">
-        <v>9889700</v>
+        <v>17607900</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="B51" t="n">
-        <v>29.45289421081543</v>
+        <v>29.31188201904297</v>
       </c>
       <c r="C51" t="n">
-        <v>29.5563042442562</v>
+        <v>29.80072717358541</v>
       </c>
       <c r="D51" t="n">
-        <v>29.14266590356487</v>
+        <v>29.29307986854401</v>
       </c>
       <c r="E51" t="n">
-        <v>29.14266590356487</v>
+        <v>29.56570567156367</v>
       </c>
       <c r="F51" t="n">
-        <v>19812000</v>
+        <v>19318400</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>45903</v>
+        <v>45915</v>
       </c>
       <c r="B52" t="n">
-        <v>29.19906997680664</v>
+        <v>29.56570625305176</v>
       </c>
       <c r="C52" t="n">
-        <v>29.47169577112148</v>
+        <v>29.65971342125195</v>
       </c>
       <c r="D52" t="n">
-        <v>29.06745851365973</v>
+        <v>29.1990714833982</v>
       </c>
       <c r="E52" t="n">
-        <v>29.25547642650249</v>
+        <v>29.42469191460788</v>
       </c>
       <c r="F52" t="n">
-        <v>29788800</v>
+        <v>21978400</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>45904</v>
+        <v>45916</v>
       </c>
       <c r="B53" t="n">
-        <v>29.19906997680664</v>
+        <v>29.64091300964355</v>
       </c>
       <c r="C53" t="n">
-        <v>29.44349254627355</v>
+        <v>29.78192555475963</v>
       </c>
       <c r="D53" t="n">
-        <v>29.07685958860904</v>
+        <v>29.46229616285823</v>
       </c>
       <c r="E53" t="n">
-        <v>29.14266532018249</v>
+        <v>29.70671874449294</v>
       </c>
       <c r="F53" t="n">
-        <v>24816500</v>
+        <v>19154700</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>45905</v>
+        <v>45917</v>
       </c>
       <c r="B54" t="n">
-        <v>28.75723075866699</v>
+        <v>29.81952857971191</v>
       </c>
       <c r="C54" t="n">
-        <v>29.22727375662746</v>
+        <v>29.88533610877261</v>
       </c>
       <c r="D54" t="n">
-        <v>28.38119671891297</v>
+        <v>29.57510599384479</v>
       </c>
       <c r="E54" t="n">
-        <v>29.21787268149964</v>
+        <v>29.65031459848559</v>
       </c>
       <c r="F54" t="n">
-        <v>46121900</v>
+        <v>29148100</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>45908</v>
+        <v>45918</v>
       </c>
       <c r="B55" t="n">
-        <v>28.87004089355469</v>
+        <v>29.52810096740723</v>
       </c>
       <c r="C55" t="n">
-        <v>29.11446347460085</v>
+        <v>29.91353608201464</v>
       </c>
       <c r="D55" t="n">
-        <v>28.68202476487657</v>
+        <v>29.3212826939577</v>
       </c>
       <c r="E55" t="n">
-        <v>28.98285200521899</v>
+        <v>29.86653249948076</v>
       </c>
       <c r="F55" t="n">
-        <v>18164200</v>
+        <v>25702900</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>45909</v>
+        <v>45919</v>
       </c>
       <c r="B56" t="n">
-        <v>29.09566307067871</v>
+        <v>29.19906997680664</v>
       </c>
       <c r="C56" t="n">
-        <v>29.28367919905826</v>
+        <v>29.56570472754286</v>
       </c>
       <c r="D56" t="n">
-        <v>28.96404980843406</v>
+        <v>29.05805743871042</v>
       </c>
       <c r="E56" t="n">
-        <v>29.01105518533279</v>
+        <v>29.54690257764424</v>
       </c>
       <c r="F56" t="n">
-        <v>31283900</v>
+        <v>48871300</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>45910</v>
+        <v>45922</v>
       </c>
       <c r="B57" t="n">
-        <v>29.62211227416992</v>
+        <v>29.49049949645996</v>
       </c>
       <c r="C57" t="n">
-        <v>29.65031550176942</v>
+        <v>29.58450666483168</v>
       </c>
       <c r="D57" t="n">
-        <v>29.0674613495496</v>
+        <v>28.99225325595955</v>
       </c>
       <c r="E57" t="n">
-        <v>29.10506385994372</v>
+        <v>29.14266687704047</v>
       </c>
       <c r="F57" t="n">
-        <v>35949600</v>
+        <v>22016100</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>45911</v>
+        <v>45923</v>
       </c>
       <c r="B58" t="n">
-        <v>29.50929832458496</v>
+        <v>29.98874473571777</v>
       </c>
       <c r="C58" t="n">
-        <v>29.59390620619104</v>
+        <v>30.16736158786953</v>
       </c>
       <c r="D58" t="n">
-        <v>29.396489011158</v>
+        <v>29.57510637028756</v>
       </c>
       <c r="E58" t="n">
-        <v>29.42469044297888</v>
+        <v>29.60330959738684</v>
       </c>
       <c r="F58" t="n">
-        <v>17607900</v>
+        <v>39895300</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>45912</v>
+        <v>45924</v>
       </c>
       <c r="B59" t="n">
-        <v>29.31188201904297</v>
+        <v>30.66560554504395</v>
       </c>
       <c r="C59" t="n">
-        <v>29.80072717358541</v>
+        <v>30.6750084136612</v>
       </c>
       <c r="D59" t="n">
-        <v>29.29307986854401</v>
+        <v>30.13915965907434</v>
       </c>
       <c r="E59" t="n">
-        <v>29.56570567156367</v>
+        <v>30.23316682838502</v>
       </c>
       <c r="F59" t="n">
-        <v>19318400</v>
+        <v>36414400</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>45915</v>
+        <v>45925</v>
       </c>
       <c r="B60" t="n">
-        <v>29.56570625305176</v>
+        <v>30.42118644714355</v>
       </c>
       <c r="C60" t="n">
-        <v>29.65971342125195</v>
+        <v>30.83482303574484</v>
       </c>
       <c r="D60" t="n">
-        <v>29.1990714833982</v>
+        <v>30.30837712046027</v>
       </c>
       <c r="E60" t="n">
-        <v>29.42469191460788</v>
+        <v>30.7408158611994</v>
       </c>
       <c r="F60" t="n">
-        <v>21978400</v>
+        <v>29556300</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>45916</v>
+        <v>45926</v>
       </c>
       <c r="B61" t="n">
-        <v>29.64091300964355</v>
+        <v>30.31777572631836</v>
       </c>
       <c r="C61" t="n">
-        <v>29.78192555475963</v>
+        <v>30.77841947804784</v>
       </c>
       <c r="D61" t="n">
-        <v>29.46229616285823</v>
+        <v>30.22376855387255</v>
       </c>
       <c r="E61" t="n">
-        <v>29.70671874449294</v>
+        <v>30.54339796078956</v>
       </c>
       <c r="F61" t="n">
-        <v>19154700</v>
+        <v>27819700</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>45917</v>
+        <v>45929</v>
       </c>
       <c r="B62" t="n">
-        <v>29.81952857971191</v>
+        <v>29.90413665771484</v>
       </c>
       <c r="C62" t="n">
-        <v>29.88533610877261</v>
+        <v>30.59040083486741</v>
       </c>
       <c r="D62" t="n">
-        <v>29.57510599384479</v>
+        <v>29.82892984566588</v>
       </c>
       <c r="E62" t="n">
-        <v>29.65031459848559</v>
+        <v>30.3271743030883</v>
       </c>
       <c r="F62" t="n">
-        <v>29148100</v>
+        <v>35720000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>45918</v>
+        <v>45930</v>
       </c>
       <c r="B63" t="n">
-        <v>29.52810096740723</v>
+        <v>29.57510566711426</v>
       </c>
       <c r="C63" t="n">
-        <v>29.91353608201464</v>
+        <v>29.98874402270987</v>
       </c>
       <c r="D63" t="n">
-        <v>29.3212826939577</v>
+        <v>29.29308057511422</v>
       </c>
       <c r="E63" t="n">
-        <v>29.86653249948076</v>
+        <v>29.79132681692421</v>
       </c>
       <c r="F63" t="n">
-        <v>25702900</v>
+        <v>48611500</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>45919</v>
+        <v>45931</v>
       </c>
       <c r="B64" t="n">
-        <v>29.19906997680664</v>
+        <v>29.49989891052246</v>
       </c>
       <c r="C64" t="n">
-        <v>29.56570472754286</v>
+        <v>29.6597136077683</v>
       </c>
       <c r="D64" t="n">
-        <v>29.05805743871042</v>
+        <v>29.42469209964629</v>
       </c>
       <c r="E64" t="n">
-        <v>29.54690257764424</v>
+        <v>29.56570643897694</v>
       </c>
       <c r="F64" t="n">
-        <v>48871300</v>
+        <v>24817000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>45922</v>
+        <v>45932</v>
       </c>
       <c r="B65" t="n">
-        <v>29.49050140380859</v>
+        <v>29.21787261962891</v>
       </c>
       <c r="C65" t="n">
-        <v>29.58450857826039</v>
+        <v>29.52810092590301</v>
       </c>
       <c r="D65" t="n">
-        <v>28.99225513108325</v>
+        <v>29.16146796205318</v>
       </c>
       <c r="E65" t="n">
-        <v>29.14266876189243</v>
+        <v>29.49989770057928</v>
       </c>
       <c r="F65" t="n">
-        <v>22016100</v>
+        <v>25497100</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>45923</v>
+        <v>45933</v>
       </c>
       <c r="B66" t="n">
-        <v>29.98874282836914</v>
+        <v>29.14266777038574</v>
       </c>
       <c r="C66" t="n">
-        <v>30.16735966916048</v>
+        <v>29.45289609750891</v>
       </c>
       <c r="D66" t="n">
-        <v>29.57510448924722</v>
+        <v>29.14266777038574</v>
       </c>
       <c r="E66" t="n">
-        <v>29.60330771455271</v>
+        <v>29.29308139607747</v>
       </c>
       <c r="F66" t="n">
-        <v>39895300</v>
+        <v>19756800</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>45924</v>
+        <v>45936</v>
       </c>
       <c r="B67" t="n">
-        <v>30.66560363769531</v>
+        <v>28.87944030761719</v>
       </c>
       <c r="C67" t="n">
-        <v>30.67500650572772</v>
+        <v>29.35888436673412</v>
       </c>
       <c r="D67" t="n">
-        <v>30.13915778446975</v>
+        <v>28.86063995098115</v>
       </c>
       <c r="E67" t="n">
-        <v>30.23316494793334</v>
+        <v>29.33068293524422</v>
       </c>
       <c r="F67" t="n">
-        <v>36414400</v>
+        <v>21245400</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>45925</v>
+        <v>45937</v>
       </c>
       <c r="B68" t="n">
-        <v>30.42118453979492</v>
+        <v>28.98285102844238</v>
       </c>
       <c r="C68" t="n">
-        <v>30.834821102462</v>
+        <v>29.0110542536759</v>
       </c>
       <c r="D68" t="n">
-        <v>30.30837522018455</v>
+        <v>28.53161018313642</v>
       </c>
       <c r="E68" t="n">
-        <v>30.74081393381063</v>
+        <v>28.87944099565787</v>
       </c>
       <c r="F68" t="n">
-        <v>29556300</v>
+        <v>29068800</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>45926</v>
+        <v>45938</v>
       </c>
       <c r="B69" t="n">
-        <v>30.31777572631836</v>
+        <v>28.81363677978516</v>
       </c>
       <c r="C69" t="n">
-        <v>30.77841947804784</v>
+        <v>29.21787406405061</v>
       </c>
       <c r="D69" t="n">
-        <v>30.22376855387255</v>
+        <v>28.67262423233884</v>
       </c>
       <c r="E69" t="n">
-        <v>30.54339796078956</v>
+        <v>29.21787406405061</v>
       </c>
       <c r="F69" t="n">
-        <v>27819700</v>
+        <v>17687400</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>45929</v>
+        <v>45939</v>
       </c>
       <c r="B70" t="n">
-        <v>29.90413665771484</v>
+        <v>28.39999771118164</v>
       </c>
       <c r="C70" t="n">
-        <v>30.59040083486741</v>
+        <v>28.99225290597609</v>
       </c>
       <c r="D70" t="n">
-        <v>29.82892984566588</v>
+        <v>28.38119735357733</v>
       </c>
       <c r="E70" t="n">
-        <v>30.3271743030883</v>
+        <v>28.82303713603482</v>
       </c>
       <c r="F70" t="n">
-        <v>35720000</v>
+        <v>22879700</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>45930</v>
+        <v>45940</v>
       </c>
       <c r="B71" t="n">
-        <v>29.57510566711426</v>
+        <v>28.14617729187012</v>
       </c>
       <c r="C71" t="n">
-        <v>29.98874402270987</v>
+        <v>28.35299558069151</v>
       </c>
       <c r="D71" t="n">
-        <v>29.29308057511422</v>
+        <v>28.08037155420294</v>
       </c>
       <c r="E71" t="n">
-        <v>29.79132681692421</v>
+        <v>28.29659091884419</v>
       </c>
       <c r="F71" t="n">
-        <v>48611500</v>
+        <v>50214400</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>45931</v>
+        <v>45943</v>
       </c>
       <c r="B72" t="n">
-        <v>29.49989891052246</v>
+        <v>28.41880035400391</v>
       </c>
       <c r="C72" t="n">
-        <v>29.6597136077683</v>
+        <v>28.45640465600731</v>
       </c>
       <c r="D72" t="n">
-        <v>29.42469209964629</v>
+        <v>28.17437777019722</v>
       </c>
       <c r="E72" t="n">
-        <v>29.56570643897694</v>
+        <v>28.34359354306891</v>
       </c>
       <c r="F72" t="n">
-        <v>24817000</v>
+        <v>13890500</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>45932</v>
+        <v>45944</v>
       </c>
       <c r="B73" t="n">
-        <v>29.21787452697754</v>
+        <v>28.22138214111328</v>
       </c>
       <c r="C73" t="n">
-        <v>29.52810285350341</v>
+        <v>28.63501868996643</v>
       </c>
       <c r="D73" t="n">
-        <v>29.1614698657197</v>
+        <v>28.08976888186751</v>
       </c>
       <c r="E73" t="n">
-        <v>29.49989962633857</v>
+        <v>28.15557640802627</v>
       </c>
       <c r="F73" t="n">
-        <v>25497100</v>
+        <v>28138200</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>45933</v>
+        <v>45945</v>
       </c>
       <c r="B74" t="n">
-        <v>29.14266586303711</v>
+        <v>27.96755790710449</v>
       </c>
       <c r="C74" t="n">
-        <v>29.45289416985625</v>
+        <v>28.36239409045707</v>
       </c>
       <c r="D74" t="n">
-        <v>29.14266586303711</v>
+        <v>27.8923511004217</v>
       </c>
       <c r="E74" t="n">
-        <v>29.29307947888447</v>
+        <v>28.24958298389703</v>
       </c>
       <c r="F74" t="n">
-        <v>19756800</v>
+        <v>40261000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>45936</v>
+        <v>45946</v>
       </c>
       <c r="B75" t="n">
-        <v>28.87944221496582</v>
+        <v>27.68553352355957</v>
       </c>
       <c r="C75" t="n">
-        <v>29.35888630574773</v>
+        <v>28.02396326557058</v>
       </c>
       <c r="D75" t="n">
-        <v>28.8606418570881</v>
+        <v>27.64792922274071</v>
       </c>
       <c r="E75" t="n">
-        <v>29.33068487239526</v>
+        <v>27.95815753220932</v>
       </c>
       <c r="F75" t="n">
-        <v>21245400</v>
+        <v>28660900</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>45937</v>
+        <v>45947</v>
       </c>
       <c r="B76" t="n">
-        <v>28.98285102844238</v>
+        <v>27.94875717163086</v>
       </c>
       <c r="C76" t="n">
-        <v>29.0110542536759</v>
+        <v>28.15557724527932</v>
       </c>
       <c r="D76" t="n">
-        <v>28.53161018313642</v>
+        <v>27.55392096829593</v>
       </c>
       <c r="E76" t="n">
-        <v>28.87944099565787</v>
+        <v>27.73253781560911</v>
       </c>
       <c r="F76" t="n">
-        <v>29068800</v>
+        <v>36238600</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>45938</v>
+        <v>45950</v>
       </c>
       <c r="B77" t="n">
-        <v>28.81363677978516</v>
+        <v>27.96755790710449</v>
       </c>
       <c r="C77" t="n">
-        <v>29.21787406405061</v>
+        <v>28.10857044550076</v>
       </c>
       <c r="D77" t="n">
-        <v>28.67262423233884</v>
+        <v>27.71373426214818</v>
       </c>
       <c r="E77" t="n">
-        <v>29.21787406405061</v>
+        <v>27.92055432532964</v>
       </c>
       <c r="F77" t="n">
-        <v>17687400</v>
+        <v>31442800</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>45939</v>
+        <v>45951</v>
       </c>
       <c r="B78" t="n">
-        <v>28.39999580383301</v>
+        <v>27.74193954467773</v>
       </c>
       <c r="C78" t="n">
-        <v>28.9922509588515</v>
+        <v>28.19318041824305</v>
       </c>
       <c r="D78" t="n">
-        <v>28.38119544749133</v>
+        <v>27.70433524201137</v>
       </c>
       <c r="E78" t="n">
-        <v>28.82303520027479</v>
+        <v>28.16497719124327</v>
       </c>
       <c r="F78" t="n">
-        <v>22879700</v>
+        <v>25509900</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>45940</v>
+        <v>45952</v>
       </c>
       <c r="B79" t="n">
-        <v>28.14617729187012</v>
+        <v>28.06156921386719</v>
       </c>
       <c r="C79" t="n">
-        <v>28.35299558069151</v>
+        <v>28.23078499134312</v>
       </c>
       <c r="D79" t="n">
-        <v>28.08037155420294</v>
+        <v>27.84534985067987</v>
       </c>
       <c r="E79" t="n">
-        <v>28.29659091884419</v>
+        <v>27.97696132512922</v>
       </c>
       <c r="F79" t="n">
-        <v>50214400</v>
+        <v>27088800</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>45943</v>
+        <v>45953</v>
       </c>
       <c r="B80" t="n">
-        <v>28.41880035400391</v>
+        <v>28.38119697570801</v>
       </c>
       <c r="C80" t="n">
-        <v>28.45640465600731</v>
+        <v>28.87944141048834</v>
       </c>
       <c r="D80" t="n">
-        <v>28.17437777019722</v>
+        <v>28.30599016707673</v>
       </c>
       <c r="E80" t="n">
-        <v>28.34359354306891</v>
+        <v>28.69142528544602</v>
       </c>
       <c r="F80" t="n">
-        <v>13890500</v>
+        <v>40060800</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>45944</v>
+        <v>45954</v>
       </c>
       <c r="B81" t="n">
-        <v>28.22138214111328</v>
+        <v>28.05216789245605</v>
       </c>
       <c r="C81" t="n">
-        <v>28.63501868996643</v>
+        <v>28.62562095708677</v>
       </c>
       <c r="D81" t="n">
-        <v>28.08976888186751</v>
+        <v>28.02396466543309</v>
       </c>
       <c r="E81" t="n">
-        <v>28.15557640802627</v>
+        <v>28.48460661504379</v>
       </c>
       <c r="F81" t="n">
-        <v>28138200</v>
+        <v>24370300</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>45945</v>
+        <v>45957</v>
       </c>
       <c r="B82" t="n">
-        <v>27.96755981445312</v>
+        <v>28.20257949829102</v>
       </c>
       <c r="C82" t="n">
-        <v>28.36239602473298</v>
+        <v>28.3529931121695</v>
       </c>
       <c r="D82" t="n">
-        <v>27.89235300264134</v>
+        <v>27.91115334553542</v>
       </c>
       <c r="E82" t="n">
-        <v>28.24958491047938</v>
+        <v>28.3529931121695</v>
       </c>
       <c r="F82" t="n">
-        <v>40261000</v>
+        <v>24771400</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>45946</v>
+        <v>45958</v>
       </c>
       <c r="B83" t="n">
-        <v>27.68553352355957</v>
+        <v>28.19318008422852</v>
       </c>
       <c r="C83" t="n">
-        <v>28.02396326557058</v>
+        <v>28.5316116319289</v>
       </c>
       <c r="D83" t="n">
-        <v>27.64792922274071</v>
+        <v>27.97696072567408</v>
       </c>
       <c r="E83" t="n">
-        <v>27.95815753220932</v>
+        <v>28.10857219730342</v>
       </c>
       <c r="F83" t="n">
-        <v>28660900</v>
+        <v>25324800</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>45947</v>
+        <v>45959</v>
       </c>
       <c r="B84" t="n">
-        <v>27.94875717163086</v>
+        <v>28.22138214111328</v>
       </c>
       <c r="C84" t="n">
-        <v>28.15557724527932</v>
+        <v>28.35299360728731</v>
       </c>
       <c r="D84" t="n">
-        <v>27.55392096829593</v>
+        <v>28.01456207361496</v>
       </c>
       <c r="E84" t="n">
-        <v>27.73253781560911</v>
+        <v>28.28718787420029</v>
       </c>
       <c r="F84" t="n">
-        <v>36238600</v>
+        <v>24854900</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>45950</v>
+        <v>45960</v>
       </c>
       <c r="B85" t="n">
-        <v>27.96755981445312</v>
+        <v>28.09917068481445</v>
       </c>
       <c r="C85" t="n">
-        <v>28.10857236246625</v>
+        <v>28.35299434164286</v>
       </c>
       <c r="D85" t="n">
-        <v>27.7137361521864</v>
+        <v>27.97696029064066</v>
       </c>
       <c r="E85" t="n">
-        <v>27.92055622947269</v>
+        <v>28.12737391104154</v>
       </c>
       <c r="F85" t="n">
-        <v>31442800</v>
+        <v>22657200</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>45951</v>
+        <v>45961</v>
       </c>
       <c r="B86" t="n">
-        <v>27.74193954467773</v>
+        <v>27.96755790710449</v>
       </c>
       <c r="C86" t="n">
-        <v>28.19318041824305</v>
+        <v>28.28718728377428</v>
       </c>
       <c r="D86" t="n">
-        <v>27.70433524201137</v>
+        <v>27.77953999386166</v>
       </c>
       <c r="E86" t="n">
-        <v>28.16497719124327</v>
+        <v>28.20257940212218</v>
       </c>
       <c r="F86" t="n">
-        <v>25509900</v>
+        <v>29516300</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>45952</v>
+        <v>45964</v>
       </c>
       <c r="B87" t="n">
-        <v>28.06156730651855</v>
+        <v>28.29659080505371</v>
       </c>
       <c r="C87" t="n">
-        <v>28.23078307249287</v>
+        <v>28.64442164363056</v>
       </c>
       <c r="D87" t="n">
-        <v>27.8453479580277</v>
+        <v>28.01456391080754</v>
       </c>
       <c r="E87" t="n">
-        <v>27.9769594235314</v>
+        <v>28.08977072399215</v>
       </c>
       <c r="F87" t="n">
-        <v>27088800</v>
+        <v>54977300</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>45953</v>
+        <v>45965</v>
       </c>
       <c r="B88" t="n">
-        <v>28.38119697570801</v>
+        <v>28.43760108947754</v>
       </c>
       <c r="C88" t="n">
-        <v>28.87944141048834</v>
+        <v>28.44700216451044</v>
       </c>
       <c r="D88" t="n">
-        <v>28.30599016707673</v>
+        <v>28.11797171064594</v>
       </c>
       <c r="E88" t="n">
-        <v>28.69142528544602</v>
+        <v>28.20257959287029</v>
       </c>
       <c r="F88" t="n">
-        <v>40060800</v>
+        <v>35035200</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>45954</v>
+        <v>45966</v>
       </c>
       <c r="B89" t="n">
-        <v>28.05216789245605</v>
+        <v>29.00165367126465</v>
       </c>
       <c r="C89" t="n">
-        <v>28.62562095708677</v>
+        <v>29.09566263056831</v>
       </c>
       <c r="D89" t="n">
-        <v>28.02396466543309</v>
+        <v>28.39999740756431</v>
       </c>
       <c r="E89" t="n">
-        <v>28.48460661504379</v>
+        <v>28.43760170851447</v>
       </c>
       <c r="F89" t="n">
-        <v>24370300</v>
+        <v>40375900</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>45957</v>
+        <v>45967</v>
       </c>
       <c r="B90" t="n">
-        <v>28.20257949829102</v>
+        <v>29.15206718444824</v>
       </c>
       <c r="C90" t="n">
-        <v>28.3529931121695</v>
+        <v>29.40589083573695</v>
       </c>
       <c r="D90" t="n">
-        <v>27.91115334553542</v>
+        <v>29.04865715027764</v>
       </c>
       <c r="E90" t="n">
-        <v>28.3529931121695</v>
+        <v>29.12386395883669</v>
       </c>
       <c r="F90" t="n">
-        <v>24771400</v>
+        <v>43435700</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>45958</v>
+        <v>45968</v>
       </c>
       <c r="B91" t="n">
-        <v>28.19318008422852</v>
+        <v>30.25196838378906</v>
       </c>
       <c r="C91" t="n">
-        <v>28.5316116319289</v>
+        <v>30.25196838378906</v>
       </c>
       <c r="D91" t="n">
-        <v>27.97696072567408</v>
+        <v>29.00165405001555</v>
       </c>
       <c r="E91" t="n">
-        <v>28.10857219730342</v>
+        <v>29.34948487298833</v>
       </c>
       <c r="F91" t="n">
-        <v>25324800</v>
+        <v>97315600</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>45959</v>
+        <v>45971</v>
       </c>
       <c r="B92" t="n">
-        <v>28.22138214111328</v>
+        <v>30.42118644714355</v>
       </c>
       <c r="C92" t="n">
-        <v>28.35299360728731</v>
+        <v>30.59980151323742</v>
       </c>
       <c r="D92" t="n">
-        <v>28.01456207361496</v>
+        <v>30.01694914153929</v>
       </c>
       <c r="E92" t="n">
-        <v>28.28718787420029</v>
+        <v>30.36477999072999</v>
       </c>
       <c r="F92" t="n">
-        <v>24854900</v>
+        <v>41064200</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>45960</v>
+        <v>45972</v>
       </c>
       <c r="B93" t="n">
-        <v>28.09916877746582</v>
+        <v>31.21085548400879</v>
       </c>
       <c r="C93" t="n">
-        <v>28.35299241706489</v>
+        <v>31.43647411263675</v>
       </c>
       <c r="D93" t="n">
-        <v>27.97695839158757</v>
+        <v>30.50579099379538</v>
       </c>
       <c r="E93" t="n">
-        <v>28.12737200177849</v>
+        <v>30.59039887606673</v>
       </c>
       <c r="F93" t="n">
-        <v>22657200</v>
+        <v>68221300</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="B94" t="n">
-        <v>27.96755981445312</v>
+        <v>30.41177940368652</v>
       </c>
       <c r="C94" t="n">
-        <v>28.28718921292119</v>
+        <v>31.26725748474499</v>
       </c>
       <c r="D94" t="n">
-        <v>27.77954188838773</v>
+        <v>30.15795935002439</v>
       </c>
       <c r="E94" t="n">
-        <v>28.20258132549895</v>
+        <v>31.26725748474499</v>
       </c>
       <c r="F94" t="n">
-        <v>29516300</v>
+        <v>67646400</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>45964</v>
+        <v>45974</v>
       </c>
       <c r="B95" t="n">
-        <v>28.29659080505371</v>
+        <v>30.54339599609375</v>
       </c>
       <c r="C95" t="n">
-        <v>28.64442164363056</v>
+        <v>30.96643183103198</v>
       </c>
       <c r="D95" t="n">
-        <v>28.01456391080754</v>
+        <v>30.38357950984352</v>
       </c>
       <c r="E95" t="n">
-        <v>28.08977072399215</v>
+        <v>30.42118381086046</v>
       </c>
       <c r="F95" t="n">
-        <v>54977300</v>
+        <v>38517200</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>45965</v>
+        <v>45975</v>
       </c>
       <c r="B96" t="n">
-        <v>28.43760299682617</v>
+        <v>30.74081039428711</v>
       </c>
       <c r="C96" t="n">
-        <v>28.44700407248961</v>
+        <v>31.18264833944727</v>
       </c>
       <c r="D96" t="n">
-        <v>28.11797359655659</v>
+        <v>30.62800108766571</v>
       </c>
       <c r="E96" t="n">
-        <v>28.20258148445571</v>
+        <v>30.64679965031661</v>
       </c>
       <c r="F96" t="n">
-        <v>35035200</v>
+        <v>27371300</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>45966</v>
+        <v>45978</v>
       </c>
       <c r="B97" t="n">
-        <v>29.00165367126465</v>
+        <v>30.9100284576416</v>
       </c>
       <c r="C97" t="n">
-        <v>29.09566263056831</v>
+        <v>31.09804637349269</v>
       </c>
       <c r="D97" t="n">
-        <v>28.39999740756431</v>
+        <v>30.76901412421742</v>
       </c>
       <c r="E97" t="n">
-        <v>28.43760170851447</v>
+        <v>30.79721555644487</v>
       </c>
       <c r="F97" t="n">
-        <v>40375900</v>
+        <v>63708200</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>45967</v>
+        <v>45979</v>
       </c>
       <c r="B98" t="n">
-        <v>29.15206909179688</v>
+        <v>31.0134391784668</v>
       </c>
       <c r="C98" t="n">
-        <v>29.40589275969264</v>
+        <v>31.18265136172766</v>
       </c>
       <c r="D98" t="n">
-        <v>29.0486590508604</v>
+        <v>30.71260835474731</v>
       </c>
       <c r="E98" t="n">
-        <v>29.12386586434005</v>
+        <v>30.74081337374374</v>
       </c>
       <c r="F98" t="n">
-        <v>43435700</v>
+        <v>26520500</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>45968</v>
+        <v>45980</v>
       </c>
       <c r="B99" t="n">
-        <v>30.25196647644043</v>
+        <v>30.85362434387207</v>
       </c>
       <c r="C99" t="n">
-        <v>30.25196647644043</v>
+        <v>31.00403797071645</v>
       </c>
       <c r="D99" t="n">
-        <v>29.00165222149766</v>
+        <v>30.59040139343033</v>
       </c>
       <c r="E99" t="n">
-        <v>29.34948302254015</v>
+        <v>30.83482219224856</v>
       </c>
       <c r="F99" t="n">
-        <v>97315600</v>
+        <v>48719300</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>45971</v>
+        <v>45982</v>
       </c>
       <c r="B100" t="n">
-        <v>30.42118453979492</v>
+        <v>30.61859893798828</v>
       </c>
       <c r="C100" t="n">
-        <v>30.59979959468997</v>
+        <v>30.77841541341311</v>
       </c>
       <c r="D100" t="n">
-        <v>30.01694725953553</v>
+        <v>30.42118175023698</v>
       </c>
       <c r="E100" t="n">
-        <v>30.36477808691793</v>
+        <v>30.60919965644248</v>
       </c>
       <c r="F100" t="n">
-        <v>41064200</v>
+        <v>40869300</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>45972</v>
+        <v>45985</v>
       </c>
       <c r="B101" t="n">
-        <v>31.21085739135742</v>
+        <v>30.59040069580078</v>
       </c>
       <c r="C101" t="n">
-        <v>31.43647603377332</v>
+        <v>30.78781790412988</v>
       </c>
       <c r="D101" t="n">
-        <v>30.50579285805632</v>
+        <v>30.42118492119193</v>
       </c>
       <c r="E101" t="n">
-        <v>30.5904007454982</v>
+        <v>30.6092028469955</v>
       </c>
       <c r="F101" t="n">
-        <v>68221300</v>
+        <v>38665600</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>45973</v>
+        <v>45986</v>
       </c>
       <c r="B102" t="n">
-        <v>30.41177940368652</v>
+        <v>30.34597587585449</v>
       </c>
       <c r="C102" t="n">
-        <v>31.26725748474499</v>
+        <v>30.49638949708493</v>
       </c>
       <c r="D102" t="n">
-        <v>30.15795935002439</v>
+        <v>30.16736082131322</v>
       </c>
       <c r="E102" t="n">
-        <v>31.26725748474499</v>
+        <v>30.41178161100883</v>
       </c>
       <c r="F102" t="n">
-        <v>67646400</v>
+        <v>28431100</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>45974</v>
+        <v>45987</v>
       </c>
       <c r="B103" t="n">
-        <v>30.54339599609375</v>
+        <v>30.29897117614746</v>
       </c>
       <c r="C103" t="n">
-        <v>30.96643183103198</v>
+        <v>30.46818694206988</v>
       </c>
       <c r="D103" t="n">
-        <v>30.38357950984352</v>
+        <v>30.17675899272717</v>
       </c>
       <c r="E103" t="n">
-        <v>30.42118381086046</v>
+        <v>30.4399855097973</v>
       </c>
       <c r="F103" t="n">
-        <v>38517200</v>
+        <v>25042100</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>45975</v>
+        <v>45988</v>
       </c>
       <c r="B104" t="n">
-        <v>30.74081230163574</v>
+        <v>30.45878982543945</v>
       </c>
       <c r="C104" t="n">
-        <v>31.18265027421025</v>
+        <v>30.45878982543945</v>
       </c>
       <c r="D104" t="n">
-        <v>30.62800298801496</v>
+        <v>30.2707718959207</v>
       </c>
       <c r="E104" t="n">
-        <v>30.64680155183224</v>
+        <v>30.34597691604196</v>
       </c>
       <c r="F104" t="n">
-        <v>27371300</v>
+        <v>16087400</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>45978</v>
+        <v>45989</v>
       </c>
       <c r="B105" t="n">
-        <v>30.9100284576416</v>
+        <v>29.88533782958984</v>
       </c>
       <c r="C105" t="n">
-        <v>31.09804637349269</v>
+        <v>30.37418302947212</v>
       </c>
       <c r="D105" t="n">
-        <v>30.76901412421742</v>
+        <v>29.41529478195041</v>
       </c>
       <c r="E105" t="n">
-        <v>30.79721555644487</v>
+        <v>30.33657872498644</v>
       </c>
       <c r="F105" t="n">
-        <v>63708200</v>
+        <v>60420500</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>45979</v>
+        <v>45992</v>
       </c>
       <c r="B106" t="n">
-        <v>31.0134391784668</v>
+        <v>29.94174003601074</v>
       </c>
       <c r="C106" t="n">
-        <v>31.18265136172766</v>
+        <v>30.24256548184863</v>
       </c>
       <c r="D106" t="n">
-        <v>30.71260835474731</v>
+        <v>29.67851530542889</v>
       </c>
       <c r="E106" t="n">
-        <v>30.74081337374374</v>
+        <v>30.03574899643796</v>
       </c>
       <c r="F106" t="n">
-        <v>26520500</v>
+        <v>29489100</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>45980</v>
+        <v>45993</v>
       </c>
       <c r="B107" t="n">
-        <v>30.85362243652344</v>
+        <v>30.14855766296387</v>
       </c>
       <c r="C107" t="n">
-        <v>31.00403605406936</v>
+        <v>30.14855766296387</v>
       </c>
       <c r="D107" t="n">
-        <v>30.59039950235395</v>
+        <v>29.55630427329339</v>
       </c>
       <c r="E107" t="n">
-        <v>30.83482028606226</v>
+        <v>30.01694619705304</v>
       </c>
       <c r="F107" t="n">
-        <v>48719300</v>
+        <v>25574100</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>45982</v>
+        <v>45994</v>
       </c>
       <c r="B108" t="n">
-        <v>30.61860084533691</v>
+        <v>30.37417984008789</v>
       </c>
       <c r="C108" t="n">
-        <v>30.77841733071732</v>
+        <v>30.55279488842395</v>
       </c>
       <c r="D108" t="n">
-        <v>30.42118364528775</v>
+        <v>30.22376622408293</v>
       </c>
       <c r="E108" t="n">
-        <v>30.6092015632056</v>
+        <v>30.22376622408293</v>
       </c>
       <c r="F108" t="n">
-        <v>40869300</v>
+        <v>36630000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B109" t="n">
-        <v>30.59040069580078</v>
+        <v>30.57159805297852</v>
       </c>
       <c r="C109" t="n">
-        <v>30.78781790412988</v>
+        <v>30.78781740902528</v>
       </c>
       <c r="D109" t="n">
-        <v>30.42118492119193</v>
+        <v>30.50579231792705</v>
       </c>
       <c r="E109" t="n">
-        <v>30.6092028469955</v>
+        <v>30.54339661971177</v>
       </c>
       <c r="F109" t="n">
-        <v>38665600</v>
+        <v>33009700</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>45986</v>
+        <v>45996</v>
       </c>
       <c r="B110" t="n">
-        <v>30.34597587585449</v>
+        <v>29.49049949645996</v>
       </c>
       <c r="C110" t="n">
-        <v>30.49638949708493</v>
+        <v>30.93823104763173</v>
       </c>
       <c r="D110" t="n">
-        <v>30.16736082131322</v>
+        <v>29.49049949645996</v>
       </c>
       <c r="E110" t="n">
-        <v>30.41178161100883</v>
+        <v>30.55279591947791</v>
       </c>
       <c r="F110" t="n">
-        <v>28431100</v>
+        <v>74495100</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>45987</v>
+        <v>45999</v>
       </c>
       <c r="B111" t="n">
-        <v>30.29897308349609</v>
+        <v>29.76312255859375</v>
       </c>
       <c r="C111" t="n">
-        <v>30.4681888600708</v>
+        <v>30.07335086626674</v>
       </c>
       <c r="D111" t="n">
-        <v>30.17676089238243</v>
+        <v>29.6033078671821</v>
       </c>
       <c r="E111" t="n">
-        <v>30.43998742602292</v>
+        <v>29.67851467531277</v>
       </c>
       <c r="F111" t="n">
-        <v>25042100</v>
+        <v>30271600</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>45988</v>
+        <v>46000</v>
       </c>
       <c r="B112" t="n">
-        <v>30.45878982543945</v>
+        <v>29.95114135742188</v>
       </c>
       <c r="C112" t="n">
-        <v>30.45878982543945</v>
+        <v>29.98874386605861</v>
       </c>
       <c r="D112" t="n">
-        <v>30.2707718959207</v>
+        <v>29.45289511821457</v>
       </c>
       <c r="E112" t="n">
-        <v>30.34597691604196</v>
+        <v>29.71611985095892</v>
       </c>
       <c r="F112" t="n">
-        <v>16087400</v>
+        <v>23863000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>45989</v>
+        <v>46001</v>
       </c>
       <c r="B113" t="n">
-        <v>29.88533592224121</v>
+        <v>30.02634811401367</v>
       </c>
       <c r="C113" t="n">
-        <v>30.3741810909243</v>
+        <v>30.0733516979934</v>
       </c>
       <c r="D113" t="n">
-        <v>29.41529290460097</v>
+        <v>29.65031406296048</v>
       </c>
       <c r="E113" t="n">
-        <v>30.33657678883861</v>
+        <v>29.96994166155185</v>
       </c>
       <c r="F113" t="n">
-        <v>60420500</v>
+        <v>22123700</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>45992</v>
+        <v>46002</v>
       </c>
       <c r="B114" t="n">
-        <v>29.94174003601074</v>
+        <v>29.52810096740723</v>
       </c>
       <c r="C114" t="n">
-        <v>30.24256548184863</v>
+        <v>29.9887428899119</v>
       </c>
       <c r="D114" t="n">
-        <v>29.67851530542889</v>
+        <v>29.37768735161271</v>
       </c>
       <c r="E114" t="n">
-        <v>30.03574899643796</v>
+        <v>29.96994073966966</v>
       </c>
       <c r="F114" t="n">
-        <v>29489100</v>
+        <v>64927900</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="B115" t="n">
-        <v>30.14855766296387</v>
+        <v>29.69731712341309</v>
       </c>
       <c r="C115" t="n">
-        <v>30.14855766296387</v>
+        <v>29.81952751544903</v>
       </c>
       <c r="D115" t="n">
-        <v>29.55630427329339</v>
+        <v>29.46229562151401</v>
       </c>
       <c r="E115" t="n">
-        <v>30.01694619705304</v>
+        <v>29.52810135515427</v>
       </c>
       <c r="F115" t="n">
-        <v>25574100</v>
+        <v>39659900</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>45994</v>
+        <v>46006</v>
       </c>
       <c r="B116" t="n">
-        <v>30.37417984008789</v>
+        <v>29.80072784423828</v>
       </c>
       <c r="C116" t="n">
-        <v>30.55279488842395</v>
+        <v>29.98874397424384</v>
       </c>
       <c r="D116" t="n">
-        <v>30.22376622408293</v>
+        <v>29.69731780723856</v>
       </c>
       <c r="E116" t="n">
-        <v>30.22376622408293</v>
+        <v>29.78192569331619</v>
       </c>
       <c r="F116" t="n">
-        <v>36630000</v>
+        <v>31898900</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>45995</v>
+        <v>46007</v>
       </c>
       <c r="B117" t="n">
-        <v>30.57159805297852</v>
+        <v>28.89824485778809</v>
       </c>
       <c r="C117" t="n">
-        <v>30.78781740902528</v>
+        <v>29.64091369528871</v>
       </c>
       <c r="D117" t="n">
-        <v>30.50579231792705</v>
+        <v>28.77603446067969</v>
       </c>
       <c r="E117" t="n">
-        <v>30.54339661971177</v>
+        <v>29.64091369528871</v>
       </c>
       <c r="F117" t="n">
-        <v>33009700</v>
+        <v>52661900</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>45996</v>
+        <v>46008</v>
       </c>
       <c r="B118" t="n">
-        <v>29.49050140380859</v>
+        <v>29.21787261962891</v>
       </c>
       <c r="C118" t="n">
-        <v>30.93823304861489</v>
+        <v>29.21787261962891</v>
       </c>
       <c r="D118" t="n">
-        <v>29.49050140380859</v>
+        <v>28.97345004603844</v>
       </c>
       <c r="E118" t="n">
-        <v>30.55279789553239</v>
+        <v>29.01105434647008</v>
       </c>
       <c r="F118" t="n">
-        <v>74495100</v>
+        <v>39337100</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>45999</v>
+        <v>46009</v>
       </c>
       <c r="B119" t="n">
-        <v>29.76312446594238</v>
+        <v>29.04865646362305</v>
       </c>
       <c r="C119" t="n">
-        <v>30.07335279349614</v>
+        <v>29.40589014063804</v>
       </c>
       <c r="D119" t="n">
-        <v>29.60330976428912</v>
+        <v>28.98285073182337</v>
       </c>
       <c r="E119" t="n">
-        <v>29.67851657723937</v>
+        <v>29.33068333385673</v>
       </c>
       <c r="F119" t="n">
-        <v>30271600</v>
+        <v>34311000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="B120" t="n">
-        <v>29.95113945007324</v>
+        <v>29.15206718444824</v>
       </c>
       <c r="C120" t="n">
-        <v>29.98874195631538</v>
+        <v>29.36828653492154</v>
       </c>
       <c r="D120" t="n">
-        <v>29.45289324259525</v>
+        <v>29.11446288363284</v>
       </c>
       <c r="E120" t="n">
-        <v>29.71611795857693</v>
+        <v>29.20847184259959</v>
       </c>
       <c r="F120" t="n">
-        <v>23863000</v>
+        <v>45807700</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="B121" t="n">
-        <v>30.02634811401367</v>
+        <v>29.2366771697998</v>
       </c>
       <c r="C121" t="n">
-        <v>30.0733516979934</v>
+        <v>29.64091446726397</v>
       </c>
       <c r="D121" t="n">
-        <v>29.65031406296048</v>
+        <v>29.2366771697998</v>
       </c>
       <c r="E121" t="n">
-        <v>29.96994166155185</v>
+        <v>29.37768972185031</v>
       </c>
       <c r="F121" t="n">
-        <v>22123700</v>
+        <v>35896900</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="B122" t="n">
-        <v>29.52810096740723</v>
+        <v>29.39390182495117</v>
       </c>
       <c r="C122" t="n">
-        <v>29.9887428899119</v>
+        <v>29.64604373642844</v>
       </c>
       <c r="D122" t="n">
-        <v>29.37768735161271</v>
+        <v>29.28722775256879</v>
       </c>
       <c r="E122" t="n">
-        <v>29.96994073966966</v>
+        <v>29.6266477779224</v>
       </c>
       <c r="F122" t="n">
-        <v>64927900</v>
+        <v>35703900</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>46003</v>
+        <v>46017</v>
       </c>
       <c r="B123" t="n">
-        <v>29.69731712341309</v>
+        <v>29.49088096618652</v>
       </c>
       <c r="C123" t="n">
-        <v>29.81952751544903</v>
+        <v>29.51027692548075</v>
       </c>
       <c r="D123" t="n">
-        <v>29.46229562151401</v>
+        <v>29.20964695522225</v>
       </c>
       <c r="E123" t="n">
-        <v>29.52810135515427</v>
+        <v>29.3939030194159</v>
       </c>
       <c r="F123" t="n">
-        <v>39659900</v>
+        <v>20178600</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>46006</v>
+        <v>46020</v>
       </c>
       <c r="B124" t="n">
-        <v>29.80072784423828</v>
+        <v>29.80120849609375</v>
       </c>
       <c r="C124" t="n">
-        <v>29.98874397424384</v>
+        <v>29.87879048247676</v>
       </c>
       <c r="D124" t="n">
-        <v>29.69731780723856</v>
+        <v>29.59755647547602</v>
       </c>
       <c r="E124" t="n">
-        <v>29.78192569331619</v>
+        <v>29.63634654381729</v>
       </c>
       <c r="F124" t="n">
-        <v>31898900</v>
+        <v>20588100</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>46007</v>
+        <v>46021</v>
       </c>
       <c r="B125" t="n">
-        <v>28.89824295043945</v>
+        <v>29.88848876953125</v>
       </c>
       <c r="C125" t="n">
-        <v>29.64091173892228</v>
+        <v>30.02425678467342</v>
       </c>
       <c r="D125" t="n">
-        <v>28.77603256139722</v>
+        <v>29.72362681555841</v>
       </c>
       <c r="E125" t="n">
-        <v>29.64091173892228</v>
+        <v>29.8690928103108</v>
       </c>
       <c r="F125" t="n">
-        <v>52661900</v>
+        <v>16880600</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>46008</v>
+        <v>46024</v>
       </c>
       <c r="B126" t="n">
-        <v>29.21787452697754</v>
+        <v>29.78181266784668</v>
       </c>
       <c r="C126" t="n">
-        <v>29.21787452697754</v>
+        <v>30.02425660757073</v>
       </c>
       <c r="D126" t="n">
-        <v>28.97345193743111</v>
+        <v>29.44239263199337</v>
       </c>
       <c r="E126" t="n">
-        <v>29.01105624031757</v>
+        <v>30.02425660757073</v>
       </c>
       <c r="F126" t="n">
-        <v>39337100</v>
+        <v>21625200</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>46009</v>
+        <v>46027</v>
       </c>
       <c r="B127" t="n">
-        <v>29.04865837097168</v>
+        <v>29.28722763061523</v>
       </c>
       <c r="C127" t="n">
-        <v>29.4058920714428</v>
+        <v>29.83999949783268</v>
       </c>
       <c r="D127" t="n">
-        <v>28.98285263485116</v>
+        <v>28.83143185612335</v>
       </c>
       <c r="E127" t="n">
-        <v>29.33068525972338</v>
+        <v>29.77211549304462</v>
       </c>
       <c r="F127" t="n">
-        <v>34311000</v>
+        <v>48211400</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>46010</v>
+        <v>46028</v>
       </c>
       <c r="B128" t="n">
-        <v>29.15206909179688</v>
+        <v>28.7441520690918</v>
       </c>
       <c r="C128" t="n">
-        <v>29.36828845641688</v>
+        <v>29.51027578428223</v>
       </c>
       <c r="D128" t="n">
-        <v>29.11446478852111</v>
+        <v>28.72475796024806</v>
       </c>
       <c r="E128" t="n">
-        <v>29.20847375363864</v>
+        <v>29.45208975835018</v>
       </c>
       <c r="F128" t="n">
-        <v>45807700</v>
+        <v>38095000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>46013</v>
+        <v>46029</v>
       </c>
       <c r="B129" t="n">
-        <v>29.2366771697998</v>
+        <v>28.92840957641602</v>
       </c>
       <c r="C129" t="n">
-        <v>29.64091446726397</v>
+        <v>28.92840957641602</v>
       </c>
       <c r="D129" t="n">
-        <v>29.2366771697998</v>
+        <v>28.63747760107253</v>
       </c>
       <c r="E129" t="n">
-        <v>29.37768972185031</v>
+        <v>28.77324560960611</v>
       </c>
       <c r="F129" t="n">
-        <v>35896900</v>
+        <v>28132900</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>46014</v>
+        <v>46030</v>
       </c>
       <c r="B130" t="n">
-        <v>29.39390182495117</v>
+        <v>29.28722763061523</v>
       </c>
       <c r="C130" t="n">
-        <v>29.64604373642844</v>
+        <v>29.42299564019133</v>
       </c>
       <c r="D130" t="n">
-        <v>29.28722775256879</v>
+        <v>28.88961973139917</v>
       </c>
       <c r="E130" t="n">
-        <v>29.6266477779224</v>
+        <v>29.00599178254999</v>
       </c>
       <c r="F130" t="n">
-        <v>35703900</v>
+        <v>34125800</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>46017</v>
+        <v>46031</v>
       </c>
       <c r="B131" t="n">
-        <v>29.49088096618652</v>
+        <v>29.38420295715332</v>
       </c>
       <c r="C131" t="n">
-        <v>29.51027692548075</v>
+        <v>29.81090478288113</v>
       </c>
       <c r="D131" t="n">
-        <v>29.20964695522225</v>
+        <v>29.22903899319782</v>
       </c>
       <c r="E131" t="n">
-        <v>29.3939030194159</v>
+        <v>29.25813293007711</v>
       </c>
       <c r="F131" t="n">
-        <v>20178600</v>
+        <v>27982800</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>46020</v>
+        <v>46034</v>
       </c>
       <c r="B132" t="n">
-        <v>29.80120849609375</v>
+        <v>29.44239234924316</v>
       </c>
       <c r="C132" t="n">
-        <v>29.87879048247676</v>
+        <v>29.64604436879937</v>
       </c>
       <c r="D132" t="n">
-        <v>29.59755647547602</v>
+        <v>29.29692450704536</v>
       </c>
       <c r="E132" t="n">
-        <v>29.63634654381729</v>
+        <v>29.38420447248386</v>
       </c>
       <c r="F132" t="n">
-        <v>20588100</v>
+        <v>18947400</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>46021</v>
+        <v>46035</v>
       </c>
       <c r="B133" t="n">
-        <v>29.88848876953125</v>
+        <v>30.19881629943848</v>
       </c>
       <c r="C133" t="n">
-        <v>30.02425678467342</v>
+        <v>30.37337623060062</v>
       </c>
       <c r="D133" t="n">
-        <v>29.72362681555841</v>
+        <v>29.44239239733645</v>
       </c>
       <c r="E133" t="n">
-        <v>29.8690928103108</v>
+        <v>29.44239239733645</v>
       </c>
       <c r="F133" t="n">
-        <v>16880600</v>
+        <v>54097100</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>46024</v>
+        <v>46036</v>
       </c>
       <c r="B134" t="n">
-        <v>29.78181266784668</v>
+        <v>31.02312660217285</v>
       </c>
       <c r="C134" t="n">
-        <v>30.02425660757073</v>
+        <v>31.54680455514679</v>
       </c>
       <c r="D134" t="n">
-        <v>29.44239263199337</v>
+        <v>30.25700470715346</v>
       </c>
       <c r="E134" t="n">
-        <v>30.02425660757073</v>
+        <v>30.40247070244063</v>
       </c>
       <c r="F134" t="n">
-        <v>21625200</v>
+        <v>82309300</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>46027</v>
+        <v>46037</v>
       </c>
       <c r="B135" t="n">
-        <v>29.28722763061523</v>
+        <v>30.82917213439941</v>
       </c>
       <c r="C135" t="n">
-        <v>29.83999949783268</v>
+        <v>30.96494014817366</v>
       </c>
       <c r="D135" t="n">
-        <v>28.83143185612335</v>
+        <v>30.48975025026335</v>
       </c>
       <c r="E135" t="n">
-        <v>29.77211549304462</v>
+        <v>30.54793627763796</v>
       </c>
       <c r="F135" t="n">
-        <v>48211400</v>
+        <v>26456600</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>46028</v>
+        <v>46038</v>
       </c>
       <c r="B136" t="n">
-        <v>28.7441520690918</v>
+        <v>31.07161521911621</v>
       </c>
       <c r="C136" t="n">
-        <v>29.51027578428223</v>
+        <v>31.22677918765084</v>
       </c>
       <c r="D136" t="n">
-        <v>28.72475796024806</v>
+        <v>30.91644940088117</v>
       </c>
       <c r="E136" t="n">
-        <v>29.45208975835018</v>
+        <v>30.98433525560293</v>
       </c>
       <c r="F136" t="n">
-        <v>38095000</v>
+        <v>70947300</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>46029</v>
+        <v>46041</v>
       </c>
       <c r="B137" t="n">
-        <v>28.92840957641602</v>
+        <v>31.19768333435059</v>
       </c>
       <c r="C137" t="n">
-        <v>28.92840957641602</v>
+        <v>31.23647525125255</v>
       </c>
       <c r="D137" t="n">
-        <v>28.63747760107253</v>
+        <v>30.94554327328942</v>
       </c>
       <c r="E137" t="n">
-        <v>28.77324560960611</v>
+        <v>30.99403131971647</v>
       </c>
       <c r="F137" t="n">
-        <v>28132900</v>
+        <v>12852900</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>46030</v>
+        <v>46042</v>
       </c>
       <c r="B138" t="n">
-        <v>29.28722763061523</v>
+        <v>31.31406021118164</v>
       </c>
       <c r="C138" t="n">
-        <v>29.42299564019133</v>
+        <v>31.53710819228805</v>
       </c>
       <c r="D138" t="n">
-        <v>28.88961973139917</v>
+        <v>30.97463832488466</v>
       </c>
       <c r="E138" t="n">
-        <v>29.00599178254999</v>
+        <v>31.1976844562906</v>
       </c>
       <c r="F138" t="n">
-        <v>34125800</v>
+        <v>26300000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>46031</v>
+        <v>46043</v>
       </c>
       <c r="B139" t="n">
-        <v>29.38420295715332</v>
+        <v>32.41960525512695</v>
       </c>
       <c r="C139" t="n">
-        <v>29.81090478288113</v>
+        <v>32.53597731516964</v>
       </c>
       <c r="D139" t="n">
-        <v>29.22903899319782</v>
+        <v>31.44982945616869</v>
       </c>
       <c r="E139" t="n">
-        <v>29.25813293007711</v>
+        <v>31.51771346614368</v>
       </c>
       <c r="F139" t="n">
-        <v>27982800</v>
+        <v>93270900</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>46034</v>
+        <v>46044</v>
       </c>
       <c r="B140" t="n">
-        <v>29.44239234924316</v>
+        <v>32.56507110595703</v>
       </c>
       <c r="C140" t="n">
-        <v>29.64604436879937</v>
+        <v>33.09844702276639</v>
       </c>
       <c r="D140" t="n">
-        <v>29.29692450704536</v>
+        <v>32.25473946588887</v>
       </c>
       <c r="E140" t="n">
-        <v>29.38420447248386</v>
+        <v>32.37111521818976</v>
       </c>
       <c r="F140" t="n">
-        <v>18947400</v>
+        <v>71516300</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>46035</v>
+        <v>46045</v>
       </c>
       <c r="B141" t="n">
-        <v>30.19881629943848</v>
+        <v>33.9809455871582</v>
       </c>
       <c r="C141" t="n">
-        <v>30.37337623060062</v>
+        <v>34.40764561575315</v>
       </c>
       <c r="D141" t="n">
-        <v>29.44239239733645</v>
+        <v>32.8560057850432</v>
       </c>
       <c r="E141" t="n">
-        <v>29.44239239733645</v>
+        <v>32.92388979642419</v>
       </c>
       <c r="F141" t="n">
-        <v>54097100</v>
+        <v>68642600</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>46036</v>
+        <v>46048</v>
       </c>
       <c r="B142" t="n">
-        <v>31.02312660217285</v>
+        <v>34.2912712097168</v>
       </c>
       <c r="C142" t="n">
-        <v>31.54680455514679</v>
+        <v>34.62099511363334</v>
       </c>
       <c r="D142" t="n">
-        <v>30.25700470715346</v>
+        <v>33.98094326478369</v>
       </c>
       <c r="E142" t="n">
-        <v>30.40247070244063</v>
+        <v>34.30096733950806</v>
       </c>
       <c r="F142" t="n">
-        <v>82309300</v>
+        <v>39869600</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>46037</v>
+        <v>46049</v>
       </c>
       <c r="B143" t="n">
-        <v>30.82917213439941</v>
+        <v>35.03799819946289</v>
       </c>
       <c r="C143" t="n">
-        <v>30.96494014817366</v>
+        <v>35.34832613745386</v>
       </c>
       <c r="D143" t="n">
-        <v>30.48975025026335</v>
+        <v>34.30096657218372</v>
       </c>
       <c r="E143" t="n">
-        <v>30.54793627763796</v>
+        <v>34.43673458262966</v>
       </c>
       <c r="F143" t="n">
-        <v>26456600</v>
+        <v>47268200</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>46038</v>
+        <v>46050</v>
       </c>
       <c r="B144" t="n">
-        <v>31.07161521911621</v>
+        <v>36.21142578125</v>
       </c>
       <c r="C144" t="n">
-        <v>31.22677918765084</v>
+        <v>36.30840187415511</v>
       </c>
       <c r="D144" t="n">
-        <v>30.91644940088117</v>
+        <v>35.3968140228843</v>
       </c>
       <c r="E144" t="n">
-        <v>30.98433525560293</v>
+        <v>35.44530206933685</v>
       </c>
       <c r="F144" t="n">
-        <v>70947300</v>
+        <v>46054700</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>46041</v>
+        <v>46051</v>
       </c>
       <c r="B145" t="n">
-        <v>31.19768333435059</v>
+        <v>36.560546875</v>
       </c>
       <c r="C145" t="n">
-        <v>31.23647525125255</v>
+        <v>37.41395057923825</v>
       </c>
       <c r="D145" t="n">
-        <v>30.94554327328942</v>
+        <v>36.43447499042595</v>
       </c>
       <c r="E145" t="n">
-        <v>30.99403131971647</v>
+        <v>36.85147886298549</v>
       </c>
       <c r="F145" t="n">
-        <v>12852900</v>
+        <v>58722800</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>46042</v>
+        <v>46052</v>
       </c>
       <c r="B146" t="n">
-        <v>31.31406021118164</v>
+        <v>36.61872863769531</v>
       </c>
       <c r="C146" t="n">
-        <v>31.53710819228805</v>
+        <v>36.83208047453306</v>
       </c>
       <c r="D146" t="n">
-        <v>30.97463832488466</v>
+        <v>35.90109669462402</v>
       </c>
       <c r="E146" t="n">
-        <v>31.1976844562906</v>
+        <v>36.10474870284149</v>
       </c>
       <c r="F146" t="n">
-        <v>26300000</v>
+        <v>45794700</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>46043</v>
+        <v>46055</v>
       </c>
       <c r="B147" t="n">
-        <v>32.41960525512695</v>
+        <v>36.11444854736328</v>
       </c>
       <c r="C147" t="n">
-        <v>32.53597731516964</v>
+        <v>36.11444854736328</v>
       </c>
       <c r="D147" t="n">
-        <v>31.44982945616869</v>
+        <v>35.51318495226501</v>
       </c>
       <c r="E147" t="n">
-        <v>31.51771346614368</v>
+        <v>35.6683489156515</v>
       </c>
       <c r="F147" t="n">
-        <v>93270900</v>
+        <v>38505600</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>46044</v>
+        <v>46056</v>
       </c>
       <c r="B148" t="n">
-        <v>32.56507110595703</v>
+        <v>36.44417572021484</v>
       </c>
       <c r="C148" t="n">
-        <v>33.09844702276639</v>
+        <v>37.16180772835154</v>
       </c>
       <c r="D148" t="n">
-        <v>32.25473946588887</v>
+        <v>36.01747200785149</v>
       </c>
       <c r="E148" t="n">
-        <v>32.37111521818976</v>
+        <v>36.37628801191983</v>
       </c>
       <c r="F148" t="n">
-        <v>71516300</v>
+        <v>57152800</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>46045</v>
+        <v>46057</v>
       </c>
       <c r="B149" t="n">
-        <v>33.9809455871582</v>
+        <v>36.385986328125</v>
       </c>
       <c r="C149" t="n">
-        <v>34.40764561575315</v>
+        <v>36.54115029905812</v>
       </c>
       <c r="D149" t="n">
-        <v>32.8560057850432</v>
+        <v>35.85261040925496</v>
       </c>
       <c r="E149" t="n">
-        <v>32.92388979642419</v>
+        <v>36.31810232205432</v>
       </c>
       <c r="F149" t="n">
-        <v>68642600</v>
+        <v>37955800</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>46048</v>
+        <v>46058</v>
       </c>
       <c r="B150" t="n">
-        <v>34.2912712097168</v>
+        <v>35.8817024230957</v>
       </c>
       <c r="C150" t="n">
-        <v>34.62099511363334</v>
+        <v>36.47326621711034</v>
       </c>
       <c r="D150" t="n">
-        <v>33.98094326478369</v>
+        <v>35.78472632873957</v>
       </c>
       <c r="E150" t="n">
-        <v>34.30096733950806</v>
+        <v>36.26961419932195</v>
       </c>
       <c r="F150" t="n">
-        <v>39869600</v>
+        <v>35933100</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>46049</v>
+        <v>46059</v>
       </c>
       <c r="B151" t="n">
-        <v>35.03799819946289</v>
+        <v>35.54228210449219</v>
       </c>
       <c r="C151" t="n">
-        <v>35.34832613745386</v>
+        <v>36.14354202329389</v>
       </c>
       <c r="D151" t="n">
-        <v>34.30096657218372</v>
+        <v>35.34832621795591</v>
       </c>
       <c r="E151" t="n">
-        <v>34.43673458262966</v>
+        <v>36.08535414751275</v>
       </c>
       <c r="F151" t="n">
-        <v>47268200</v>
+        <v>27681100</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>46050</v>
+        <v>46062</v>
       </c>
       <c r="B152" t="n">
-        <v>36.21142578125</v>
+        <v>36.19203186035156</v>
       </c>
       <c r="C152" t="n">
-        <v>36.30840187415511</v>
+        <v>36.31810374774653</v>
       </c>
       <c r="D152" t="n">
-        <v>35.3968140228843</v>
+        <v>35.44530406485983</v>
       </c>
       <c r="E152" t="n">
-        <v>35.44530206933685</v>
+        <v>35.55197999270165</v>
       </c>
       <c r="F152" t="n">
-        <v>46054700</v>
+        <v>27089800</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>46051</v>
+        <v>46063</v>
       </c>
       <c r="B153" t="n">
-        <v>36.560546875</v>
+        <v>36.22112274169922</v>
       </c>
       <c r="C153" t="n">
-        <v>37.41395057923825</v>
+        <v>36.44417441941928</v>
       </c>
       <c r="D153" t="n">
-        <v>36.43447499042595</v>
+        <v>35.79442274396702</v>
       </c>
       <c r="E153" t="n">
-        <v>36.85147886298549</v>
+        <v>36.19203065304047</v>
       </c>
       <c r="F153" t="n">
-        <v>58722800</v>
+        <v>24585300</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>46052</v>
+        <v>46064</v>
       </c>
       <c r="B154" t="n">
-        <v>36.61872863769531</v>
+        <v>36.92906188964844</v>
       </c>
       <c r="C154" t="n">
-        <v>36.83208047453306</v>
+        <v>37.29757400662855</v>
       </c>
       <c r="D154" t="n">
-        <v>35.90109669462402</v>
+        <v>36.55084624422012</v>
       </c>
       <c r="E154" t="n">
-        <v>36.10474870284149</v>
+        <v>36.58963816160778</v>
       </c>
       <c r="F154" t="n">
-        <v>45794700</v>
+        <v>55863800</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="B155" t="n">
-        <v>36.11444854736328</v>
+        <v>35.98837661743164</v>
       </c>
       <c r="C155" t="n">
-        <v>36.11444854736328</v>
+        <v>36.89996443854407</v>
       </c>
       <c r="D155" t="n">
-        <v>35.51318495226501</v>
+        <v>35.6877448203304</v>
       </c>
       <c r="E155" t="n">
-        <v>35.6683489156515</v>
+        <v>36.89996443854407</v>
       </c>
       <c r="F155" t="n">
-        <v>38505600</v>
+        <v>39856000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>46056</v>
+        <v>46066</v>
       </c>
       <c r="B156" t="n">
-        <v>36.44417572021484</v>
+        <v>35.77502822875977</v>
       </c>
       <c r="C156" t="n">
-        <v>37.16180772835154</v>
+        <v>36.03686813545773</v>
       </c>
       <c r="D156" t="n">
-        <v>36.01747200785149</v>
+        <v>35.42590835316248</v>
       </c>
       <c r="E156" t="n">
-        <v>36.37628801191983</v>
+        <v>36.03686813545773</v>
       </c>
       <c r="F156" t="n">
-        <v>57152800</v>
+        <v>27507000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>46057</v>
+        <v>46071</v>
       </c>
       <c r="B157" t="n">
-        <v>36.385986328125</v>
+        <v>36.06595993041992</v>
       </c>
       <c r="C157" t="n">
-        <v>36.54115029905812</v>
+        <v>36.25991582632166</v>
       </c>
       <c r="D157" t="n">
-        <v>35.85261040925496</v>
+        <v>35.73623601720728</v>
       </c>
       <c r="E157" t="n">
-        <v>36.31810232205432</v>
+        <v>35.94958787263928</v>
       </c>
       <c r="F157" t="n">
-        <v>37955800</v>
+        <v>32276700</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>46058</v>
+        <v>46072</v>
       </c>
       <c r="B158" t="n">
-        <v>35.8817024230957</v>
+        <v>36.66722106933594</v>
       </c>
       <c r="C158" t="n">
-        <v>36.47326621711034</v>
+        <v>37.08422492220805</v>
       </c>
       <c r="D158" t="n">
-        <v>35.78472632873957</v>
+        <v>36.30840139167339</v>
       </c>
       <c r="E158" t="n">
-        <v>36.26961419932195</v>
+        <v>36.36658926628372</v>
       </c>
       <c r="F158" t="n">
-        <v>35933100</v>
+        <v>48355000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>46059</v>
+        <v>46073</v>
       </c>
       <c r="B159" t="n">
-        <v>35.54228210449219</v>
+        <v>36.82238388061523</v>
       </c>
       <c r="C159" t="n">
-        <v>36.14354202329389</v>
+        <v>36.82238388061523</v>
       </c>
       <c r="D159" t="n">
-        <v>35.34832621795591</v>
+        <v>36.31810008134505</v>
       </c>
       <c r="E159" t="n">
-        <v>36.08535414751275</v>
+        <v>36.53144821608966</v>
       </c>
       <c r="F159" t="n">
-        <v>27681100</v>
+        <v>51949800</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>46062</v>
+        <v>46076</v>
       </c>
       <c r="B160" t="n">
-        <v>36.19203186035156</v>
+        <v>37.42364883422852</v>
       </c>
       <c r="C160" t="n">
-        <v>36.31810374774653</v>
+        <v>38.06370072390281</v>
       </c>
       <c r="D160" t="n">
-        <v>35.44530406485983</v>
+        <v>36.70601310367194</v>
       </c>
       <c r="E160" t="n">
-        <v>35.55197999270165</v>
+        <v>36.82238886499537</v>
       </c>
       <c r="F160" t="n">
-        <v>27089800</v>
+        <v>55061500</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>46063</v>
+        <v>46077</v>
       </c>
       <c r="B161" t="n">
-        <v>36.22112274169922</v>
+        <v>38.37402725219727</v>
       </c>
       <c r="C161" t="n">
-        <v>36.44417441941928</v>
+        <v>38.46130722022217</v>
       </c>
       <c r="D161" t="n">
-        <v>35.79442274396702</v>
+        <v>37.68548733744582</v>
       </c>
       <c r="E161" t="n">
-        <v>36.19203065304047</v>
+        <v>37.68548733744582</v>
       </c>
       <c r="F161" t="n">
-        <v>24585300</v>
+        <v>43263600</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>46064</v>
+        <v>46078</v>
       </c>
       <c r="B162" t="n">
-        <v>36.92906188964844</v>
+        <v>38.37402725219727</v>
       </c>
       <c r="C162" t="n">
-        <v>37.29757400662855</v>
+        <v>38.76193904328594</v>
       </c>
       <c r="D162" t="n">
-        <v>36.55084624422012</v>
+        <v>37.85034744404786</v>
       </c>
       <c r="E162" t="n">
-        <v>36.58963816160778</v>
+        <v>38.73284325434363</v>
       </c>
       <c r="F162" t="n">
-        <v>55863800</v>
+        <v>26012300</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>46065</v>
+        <v>46079</v>
       </c>
       <c r="B163" t="n">
-        <v>35.98837661743164</v>
+        <v>38.41281890869141</v>
       </c>
       <c r="C163" t="n">
-        <v>36.89996443854407</v>
+        <v>38.59707497352885</v>
       </c>
       <c r="D163" t="n">
-        <v>35.6877448203304</v>
+        <v>37.7921630067116</v>
       </c>
       <c r="E163" t="n">
-        <v>36.89996443854407</v>
+        <v>38.11218708768201</v>
       </c>
       <c r="F163" t="n">
-        <v>39856000</v>
+        <v>29919100</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>46066</v>
+        <v>46080</v>
       </c>
       <c r="B164" t="n">
-        <v>35.77502822875977</v>
+        <v>38.14128112792969</v>
       </c>
       <c r="C164" t="n">
-        <v>36.03686813545773</v>
+        <v>39.05286897974784</v>
       </c>
       <c r="D164" t="n">
-        <v>35.42590835316248</v>
+        <v>38.14128112792969</v>
       </c>
       <c r="E164" t="n">
-        <v>36.03686813545773</v>
+        <v>38.71344525557453</v>
       </c>
       <c r="F164" t="n">
-        <v>27507000</v>
+        <v>38799000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>46071</v>
+        <v>46083</v>
       </c>
       <c r="B165" t="n">
-        <v>36.06595993041992</v>
+        <v>39.88687515258789</v>
       </c>
       <c r="C165" t="n">
-        <v>36.25991582632166</v>
+        <v>40.2747832088216</v>
       </c>
       <c r="D165" t="n">
-        <v>35.73623601720728</v>
+        <v>39.29531138997576</v>
       </c>
       <c r="E165" t="n">
-        <v>35.94958787263928</v>
+        <v>40.05173524412206</v>
       </c>
       <c r="F165" t="n">
-        <v>32276700</v>
+        <v>83817000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>46072</v>
+        <v>46084</v>
       </c>
       <c r="B166" t="n">
-        <v>36.66722106933594</v>
+        <v>39.71231842041016</v>
       </c>
       <c r="C166" t="n">
-        <v>37.08422492220805</v>
+        <v>40.73058223644099</v>
       </c>
       <c r="D166" t="n">
-        <v>36.30840139167339</v>
+        <v>39.5183625270231</v>
       </c>
       <c r="E166" t="n">
-        <v>36.36658926628372</v>
+        <v>40.43965024606089</v>
       </c>
       <c r="F166" t="n">
-        <v>48355000</v>
+        <v>93893800</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>46073</v>
+        <v>46085</v>
       </c>
       <c r="B167" t="n">
-        <v>36.82238388061523</v>
+        <v>39.27591705322266</v>
       </c>
       <c r="C167" t="n">
-        <v>36.82238388061523</v>
+        <v>39.92566501641542</v>
       </c>
       <c r="D167" t="n">
-        <v>36.31810008134505</v>
+        <v>38.72314518324048</v>
       </c>
       <c r="E167" t="n">
-        <v>36.53144821608966</v>
+        <v>39.71231687147196</v>
       </c>
       <c r="F167" t="n">
-        <v>51949800</v>
+        <v>50915600</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="B168" t="n">
-        <v>37.42364883422852</v>
+        <v>39.46017456054688</v>
       </c>
       <c r="C168" t="n">
-        <v>38.06370072390281</v>
+        <v>39.53775839748781</v>
       </c>
       <c r="D168" t="n">
-        <v>36.70601310367194</v>
+        <v>38.77163465500042</v>
       </c>
       <c r="E168" t="n">
-        <v>36.82238886499537</v>
+        <v>39.30501058606597</v>
       </c>
       <c r="F168" t="n">
-        <v>55061500</v>
+        <v>53107600</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>46077</v>
+        <v>46087</v>
       </c>
       <c r="B169" t="n">
-        <v>38.37402725219727</v>
+        <v>40.88574600219727</v>
       </c>
       <c r="C169" t="n">
-        <v>38.46130722022217</v>
+        <v>41.8167298464133</v>
       </c>
       <c r="D169" t="n">
-        <v>37.68548733744582</v>
+        <v>40.16811031015515</v>
       </c>
       <c r="E169" t="n">
-        <v>37.68548733744582</v>
+        <v>40.63360593166411</v>
       </c>
       <c r="F169" t="n">
-        <v>43263600</v>
+        <v>87228000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="B170" t="n">
-        <v>38.37402725219727</v>
+        <v>41.85552215576172</v>
       </c>
       <c r="C170" t="n">
-        <v>38.76193904328594</v>
+        <v>42.93197385417998</v>
       </c>
       <c r="D170" t="n">
-        <v>37.85034744404786</v>
+        <v>41.38033039992446</v>
       </c>
       <c r="E170" t="n">
-        <v>38.73284325434363</v>
+        <v>41.94280212318485</v>
       </c>
       <c r="F170" t="n">
-        <v>26012300</v>
+        <v>107124400</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>46079</v>
+        <v>46091</v>
       </c>
       <c r="B171" t="n">
-        <v>38.41281890869141</v>
+        <v>41.63247299194336</v>
       </c>
       <c r="C171" t="n">
-        <v>38.59707497352885</v>
+        <v>41.79733309273498</v>
       </c>
       <c r="D171" t="n">
-        <v>37.7921630067116</v>
+        <v>40.75967334245573</v>
       </c>
       <c r="E171" t="n">
-        <v>38.11218708768201</v>
+        <v>41.03121306640792</v>
       </c>
       <c r="F171" t="n">
-        <v>29919100</v>
+        <v>56706200</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>46080</v>
+        <v>46092</v>
       </c>
       <c r="B172" t="n">
-        <v>38.14128112792969</v>
+        <v>43.44595336914062</v>
       </c>
       <c r="C172" t="n">
-        <v>39.05286897974784</v>
+        <v>43.52353720576205</v>
       </c>
       <c r="D172" t="n">
-        <v>38.14128112792969</v>
+        <v>41.92340571975425</v>
       </c>
       <c r="E172" t="n">
-        <v>38.71344525557453</v>
+        <v>41.9428016789096</v>
       </c>
       <c r="F172" t="n">
-        <v>38799000</v>
+        <v>73234300</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="B173" t="n">
-        <v>39.88687515258789</v>
+        <v>43.63991165161133</v>
       </c>
       <c r="C173" t="n">
-        <v>40.2747832088216</v>
+        <v>44.69696743737085</v>
       </c>
       <c r="D173" t="n">
-        <v>39.29531138997576</v>
+        <v>42.86409173990736</v>
       </c>
       <c r="E173" t="n">
-        <v>40.05173524412206</v>
+        <v>44.01812362735444</v>
       </c>
       <c r="F173" t="n">
-        <v>83817000</v>
+        <v>86124400</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>46084</v>
+        <v>46094</v>
       </c>
       <c r="B174" t="n">
-        <v>39.71231842041016</v>
+        <v>43.31988143920898</v>
       </c>
       <c r="C174" t="n">
-        <v>40.73058223644099</v>
+        <v>43.96963312233328</v>
       </c>
       <c r="D174" t="n">
-        <v>39.5183625270231</v>
+        <v>42.95136931384393</v>
       </c>
       <c r="E174" t="n">
-        <v>40.43965024606089</v>
+        <v>43.26169726120447</v>
       </c>
       <c r="F174" t="n">
-        <v>93893800</v>
+        <v>42520400</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B175" t="n">
-        <v>39.27591705322266</v>
+        <v>44.47391891479492</v>
       </c>
       <c r="C175" t="n">
-        <v>39.92566501641542</v>
+        <v>44.5999908050096</v>
       </c>
       <c r="D175" t="n">
-        <v>38.72314518324048</v>
+        <v>43.44595523189268</v>
       </c>
       <c r="E175" t="n">
-        <v>39.71231687147196</v>
+        <v>43.52353907184052</v>
       </c>
       <c r="F175" t="n">
-        <v>50915600</v>
+        <v>40474100</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>46086</v>
+        <v>46098</v>
       </c>
       <c r="B176" t="n">
-        <v>39.46017456054688</v>
+        <v>44.97819900512695</v>
       </c>
       <c r="C176" t="n">
-        <v>39.53775839748781</v>
+        <v>45.83159897659459</v>
       </c>
       <c r="D176" t="n">
-        <v>38.77163465500042</v>
+        <v>44.41572731086798</v>
       </c>
       <c r="E176" t="n">
-        <v>39.30501058606597</v>
+        <v>44.46421535706942</v>
       </c>
       <c r="F176" t="n">
-        <v>53107600</v>
+        <v>51025600</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="B177" t="n">
-        <v>40.88574600219727</v>
+        <v>45.5794563293457</v>
       </c>
       <c r="C177" t="n">
-        <v>41.8167298464133</v>
+        <v>45.72492415909321</v>
       </c>
       <c r="D177" t="n">
-        <v>40.16811031015515</v>
+        <v>45.14305653950377</v>
       </c>
       <c r="E177" t="n">
-        <v>40.63360593166411</v>
+        <v>45.28852436925127</v>
       </c>
       <c r="F177" t="n">
-        <v>87228000</v>
+        <v>55074700</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>46090</v>
+        <v>46100</v>
       </c>
       <c r="B178" t="n">
-        <v>41.85552215576172</v>
+        <v>45.36610794067383</v>
       </c>
       <c r="C178" t="n">
-        <v>42.93197385417998</v>
+        <v>46.6753074095245</v>
       </c>
       <c r="D178" t="n">
-        <v>41.38033039992446</v>
+        <v>45.27882797608378</v>
       </c>
       <c r="E178" t="n">
-        <v>41.94280212318485</v>
+        <v>45.77341567522765</v>
       </c>
       <c r="F178" t="n">
-        <v>107124400</v>
+        <v>84865000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>46091</v>
+        <v>46101</v>
       </c>
       <c r="B179" t="n">
-        <v>41.63247299194336</v>
+        <v>44.28965377807617</v>
       </c>
       <c r="C179" t="n">
-        <v>41.79733309273498</v>
+        <v>45.82190113677482</v>
       </c>
       <c r="D179" t="n">
-        <v>40.75967334245573</v>
+        <v>43.56232201400038</v>
       </c>
       <c r="E179" t="n">
-        <v>41.03121306640792</v>
+        <v>45.37580520933116</v>
       </c>
       <c r="F179" t="n">
-        <v>56706200</v>
+        <v>78125700</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>46092</v>
+        <v>46104</v>
       </c>
       <c r="B180" t="n">
-        <v>43.44595336914062</v>
+        <v>44.63877868652344</v>
       </c>
       <c r="C180" t="n">
-        <v>43.52353720576205</v>
+        <v>44.78424653562016</v>
       </c>
       <c r="D180" t="n">
-        <v>41.92340571975425</v>
+        <v>42.9804629639459</v>
       </c>
       <c r="E180" t="n">
-        <v>41.9428016789096</v>
+        <v>43.07743906374301</v>
       </c>
       <c r="F180" t="n">
-        <v>73234300</v>
+        <v>65252400</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>46093</v>
+        <v>46105</v>
       </c>
       <c r="B181" t="n">
-        <v>43.63991165161133</v>
+        <v>45.84130096435547</v>
       </c>
       <c r="C181" t="n">
-        <v>44.69696743737085</v>
+        <v>46.50074878207379</v>
       </c>
       <c r="D181" t="n">
-        <v>42.86409173990736</v>
+        <v>44.9685012940221</v>
       </c>
       <c r="E181" t="n">
-        <v>44.01812362735444</v>
+        <v>44.99759708263386</v>
       </c>
       <c r="F181" t="n">
-        <v>86124400</v>
+        <v>57455300</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>46094</v>
+        <v>46106</v>
       </c>
       <c r="B182" t="n">
-        <v>43.31988143920898</v>
+        <v>46.06434631347656</v>
       </c>
       <c r="C182" t="n">
-        <v>43.96963312233328</v>
+        <v>46.11283435918954</v>
       </c>
       <c r="D182" t="n">
-        <v>42.95136931384393</v>
+        <v>44.90061471936122</v>
       </c>
       <c r="E182" t="n">
-        <v>43.26169726120447</v>
+        <v>45.0945706016139</v>
       </c>
       <c r="F182" t="n">
-        <v>42520400</v>
+        <v>40532900</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>46097</v>
+        <v>46107</v>
       </c>
       <c r="B183" t="n">
-        <v>44.47391891479492</v>
+        <v>46.56863021850586</v>
       </c>
       <c r="C183" t="n">
-        <v>44.5999908050096</v>
+        <v>47.00503002957635</v>
       </c>
       <c r="D183" t="n">
-        <v>43.44595523189268</v>
+        <v>46.08374236162771</v>
       </c>
       <c r="E183" t="n">
-        <v>43.52353907184052</v>
+        <v>46.16132249503981</v>
       </c>
       <c r="F183" t="n">
-        <v>40474100</v>
+        <v>59986800</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="B184" t="n">
-        <v>44.97819900512695</v>
+        <v>47.91661834716797</v>
       </c>
       <c r="C184" t="n">
-        <v>45.83159897659459</v>
+        <v>47.9457104350629</v>
       </c>
       <c r="D184" t="n">
-        <v>44.41572731086798</v>
+        <v>46.67530660497371</v>
       </c>
       <c r="E184" t="n">
-        <v>44.46421535706942</v>
+        <v>47.03412258681409</v>
       </c>
       <c r="F184" t="n">
-        <v>51025600</v>
+        <v>54170900</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>46099</v>
+        <v>46111</v>
       </c>
       <c r="B185" t="n">
-        <v>45.5794563293457</v>
+        <v>48.16875839233398</v>
       </c>
       <c r="C185" t="n">
-        <v>45.72492415909321</v>
+        <v>49.15793007385836</v>
       </c>
       <c r="D185" t="n">
-        <v>45.14305653950377</v>
+        <v>47.99420216561867</v>
       </c>
       <c r="E185" t="n">
-        <v>45.28852436925127</v>
+        <v>48.24634222589705</v>
       </c>
       <c r="F185" t="n">
-        <v>55074700</v>
+        <v>51454300</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>46100</v>
+        <v>46112</v>
       </c>
       <c r="B186" t="n">
-        <v>45.36610794067383</v>
+        <v>47.19898223876953</v>
       </c>
       <c r="C186" t="n">
-        <v>46.6753074095245</v>
+        <v>49.02216161746647</v>
       </c>
       <c r="D186" t="n">
-        <v>45.27882797608378</v>
+        <v>46.20981426566667</v>
       </c>
       <c r="E186" t="n">
-        <v>45.77341567522765</v>
+        <v>48.55666971853548</v>
       </c>
       <c r="F186" t="n">
-        <v>84865000</v>
+        <v>78931700</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>46101</v>
+        <v>46113</v>
       </c>
       <c r="B187" t="n">
-        <v>44.28965377807617</v>
+        <v>45.93827438354492</v>
       </c>
       <c r="C187" t="n">
-        <v>45.82190113677482</v>
+        <v>46.61711812096706</v>
       </c>
       <c r="D187" t="n">
-        <v>43.56232201400038</v>
+        <v>45.35641043684066</v>
       </c>
       <c r="E187" t="n">
-        <v>45.37580520933116</v>
+        <v>46.25830214381279</v>
       </c>
       <c r="F187" t="n">
-        <v>78125700</v>
+        <v>66488400</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>46104</v>
+        <v>46114</v>
       </c>
       <c r="B188" t="n">
-        <v>44.63877868652344</v>
+        <v>46.6947021484375</v>
       </c>
       <c r="C188" t="n">
-        <v>44.78424653562016</v>
+        <v>47.96510596723777</v>
       </c>
       <c r="D188" t="n">
-        <v>42.9804629639459</v>
+        <v>46.50074626559295</v>
       </c>
       <c r="E188" t="n">
-        <v>43.07743906374301</v>
+        <v>47.80994200084229</v>
       </c>
       <c r="F188" t="n">
-        <v>65252400</v>
+        <v>38536900</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>46105</v>
+        <v>46118</v>
       </c>
       <c r="B189" t="n">
-        <v>45.84130096435547</v>
+        <v>47.46082305908203</v>
       </c>
       <c r="C189" t="n">
-        <v>46.50074878207379</v>
+        <v>47.51901093486821</v>
       </c>
       <c r="D189" t="n">
-        <v>44.9685012940221</v>
+        <v>46.43286314933203</v>
       </c>
       <c r="E189" t="n">
-        <v>44.99759708263386</v>
+        <v>46.53953907190628</v>
       </c>
       <c r="F189" t="n">
-        <v>57455300</v>
+        <v>27848100</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>46106</v>
+        <v>46119</v>
       </c>
       <c r="B190" t="n">
-        <v>46.06434631347656</v>
+        <v>47.04381942749023</v>
       </c>
       <c r="C190" t="n">
-        <v>46.11283435918954</v>
+        <v>48.06208691201583</v>
       </c>
       <c r="D190" t="n">
-        <v>44.90061471936122</v>
+        <v>46.93714720379597</v>
       </c>
       <c r="E190" t="n">
-        <v>45.0945706016139</v>
+        <v>47.60629113130059</v>
       </c>
       <c r="F190" t="n">
-        <v>40532900</v>
+        <v>33362800</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="B191" t="n">
-        <v>46.56863021850586</v>
+        <v>45.20124816894531</v>
       </c>
       <c r="C191" t="n">
-        <v>47.00503002957635</v>
+        <v>45.23034025755306</v>
       </c>
       <c r="D191" t="n">
-        <v>46.08374236162771</v>
+        <v>43.18411283905469</v>
       </c>
       <c r="E191" t="n">
-        <v>46.16132249503981</v>
+        <v>43.34897663976734</v>
       </c>
       <c r="F191" t="n">
-        <v>59986800</v>
+        <v>87580500</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>46108</v>
+        <v>46121</v>
       </c>
       <c r="B192" t="n">
-        <v>47.91661834716797</v>
+        <v>46.4522590637207</v>
       </c>
       <c r="C192" t="n">
-        <v>47.9457104350629</v>
+        <v>47.08261107016735</v>
       </c>
       <c r="D192" t="n">
-        <v>46.67530660497371</v>
+        <v>45.60855151292778</v>
       </c>
       <c r="E192" t="n">
-        <v>47.03412258681409</v>
+        <v>46.10313920813753</v>
       </c>
       <c r="F192" t="n">
-        <v>54170900</v>
+        <v>58206500</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>46111</v>
+        <v>46122</v>
       </c>
       <c r="B193" t="n">
-        <v>48.16875839233398</v>
+        <v>47.54810333251953</v>
       </c>
       <c r="C193" t="n">
-        <v>49.15793007385836</v>
+        <v>47.54810333251953</v>
       </c>
       <c r="D193" t="n">
-        <v>47.99420216561867</v>
+        <v>46.09343972300512</v>
       </c>
       <c r="E193" t="n">
-        <v>48.24634222589705</v>
+        <v>46.09343972300512</v>
       </c>
       <c r="F193" t="n">
-        <v>51454300</v>
+        <v>42860900</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>46112</v>
+        <v>46125</v>
       </c>
       <c r="B194" t="n">
-        <v>47.19898223876953</v>
+        <v>48.27543258666992</v>
       </c>
       <c r="C194" t="n">
-        <v>49.02216161746647</v>
+        <v>48.72153221489623</v>
       </c>
       <c r="D194" t="n">
-        <v>46.20981426566667</v>
+        <v>47.76145265560563</v>
       </c>
       <c r="E194" t="n">
-        <v>48.55666971853548</v>
+        <v>48.24634049982497</v>
       </c>
       <c r="F194" t="n">
-        <v>78931700</v>
+        <v>60941100</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="B195" t="n">
-        <v>45.93827438354492</v>
+        <v>46.43286514282227</v>
       </c>
       <c r="C195" t="n">
-        <v>46.61711812096706</v>
+        <v>48.14936870850001</v>
       </c>
       <c r="D195" t="n">
-        <v>45.35641043684066</v>
+        <v>46.22920941852755</v>
       </c>
       <c r="E195" t="n">
-        <v>46.25830214381279</v>
+        <v>48.11057678964378</v>
       </c>
       <c r="F195" t="n">
-        <v>66488400</v>
+        <v>58646800</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>46114</v>
+        <v>46127</v>
       </c>
       <c r="B196" t="n">
-        <v>46.6947021484375</v>
+        <v>45.47278594970703</v>
       </c>
       <c r="C196" t="n">
-        <v>47.96510596723777</v>
+        <v>46.64621376126109</v>
       </c>
       <c r="D196" t="n">
-        <v>46.50074626559295</v>
+        <v>45.31762197214121</v>
       </c>
       <c r="E196" t="n">
-        <v>47.80994200084229</v>
+        <v>46.50074961320622</v>
       </c>
       <c r="F196" t="n">
-        <v>38536900</v>
+        <v>61852100</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>46118</v>
+        <v>46128</v>
       </c>
       <c r="B197" t="n">
-        <v>47.46082305908203</v>
+        <v>47.1117057800293</v>
       </c>
       <c r="C197" t="n">
-        <v>47.51901093486821</v>
+        <v>47.20868187129476</v>
       </c>
       <c r="D197" t="n">
-        <v>46.43286314933203</v>
+        <v>45.34671058391167</v>
       </c>
       <c r="E197" t="n">
-        <v>46.53953907190628</v>
+        <v>45.86069422594074</v>
       </c>
       <c r="F197" t="n">
-        <v>27848100</v>
+        <v>54484300</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>46119</v>
+        <v>46129</v>
       </c>
       <c r="B198" t="n">
-        <v>47.04381942749023</v>
+        <v>44.82303619384766</v>
       </c>
       <c r="C198" t="n">
-        <v>48.06208691201583</v>
+        <v>45.14306026655282</v>
       </c>
       <c r="D198" t="n">
-        <v>46.93714720379597</v>
+        <v>43.51383671623324</v>
       </c>
       <c r="E198" t="n">
-        <v>47.60629113130059</v>
+        <v>45.09457221910063</v>
       </c>
       <c r="F198" t="n">
-        <v>33362800</v>
+        <v>105186900</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>46120</v>
+        <v>46132</v>
       </c>
       <c r="B199" t="n">
-        <v>45.20124816894531</v>
+        <v>45.59885787963867</v>
       </c>
       <c r="C199" t="n">
-        <v>45.23034025755306</v>
+        <v>46.0449538531271</v>
       </c>
       <c r="D199" t="n">
-        <v>43.18411283905469</v>
+        <v>45.10427015735281</v>
       </c>
       <c r="E199" t="n">
-        <v>43.34897663976734</v>
+        <v>45.81220973626403</v>
       </c>
       <c r="F199" t="n">
-        <v>87580500</v>
+        <v>41904500</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>46121</v>
+        <v>46134</v>
       </c>
       <c r="B200" t="n">
-        <v>46.4522590637207</v>
+        <v>46.22920608520508</v>
       </c>
       <c r="C200" t="n">
-        <v>47.08261107016735</v>
+        <v>46.52983788556254</v>
       </c>
       <c r="D200" t="n">
-        <v>45.60855151292778</v>
+        <v>45.82190206478599</v>
       </c>
       <c r="E200" t="n">
-        <v>46.10313920813753</v>
+        <v>46.20011399786107</v>
       </c>
       <c r="F200" t="n">
-        <v>58206500</v>
+        <v>51063000</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>46122</v>
+        <v>46135</v>
       </c>
       <c r="B201" t="n">
-        <v>47.54810333251953</v>
+        <v>46.97968673706055</v>
       </c>
       <c r="C201" t="n">
-        <v>47.54810333251953</v>
+        <v>47.28455940328853</v>
       </c>
       <c r="D201" t="n">
-        <v>46.09343972300512</v>
+        <v>46.12408119195152</v>
       </c>
       <c r="E201" t="n">
-        <v>46.09343972300512</v>
+        <v>46.57646998577134</v>
       </c>
       <c r="F201" t="n">
-        <v>42860900</v>
+        <v>38666800</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>46125</v>
+        <v>46136</v>
       </c>
       <c r="B202" t="n">
-        <v>48.27543258666992</v>
+        <v>46.37977981567383</v>
       </c>
       <c r="C202" t="n">
-        <v>48.72153221489623</v>
+        <v>46.73382453780353</v>
       </c>
       <c r="D202" t="n">
-        <v>47.76145265560563</v>
+        <v>45.68152703124387</v>
       </c>
       <c r="E202" t="n">
-        <v>48.24634049982497</v>
+        <v>46.71415496973115</v>
       </c>
       <c r="F202" t="n">
-        <v>60941100</v>
+        <v>34880200</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>46126</v>
+        <v>46139</v>
       </c>
       <c r="B203" t="n">
-        <v>46.43286514282227</v>
+        <v>46.5863037109375</v>
       </c>
       <c r="C203" t="n">
-        <v>48.14936870850001</v>
+        <v>47.37306765998913</v>
       </c>
       <c r="D203" t="n">
-        <v>46.22920941852755</v>
+        <v>46.38961178577799</v>
       </c>
       <c r="E203" t="n">
-        <v>48.11057678964378</v>
+        <v>46.43878758075769</v>
       </c>
       <c r="F203" t="n">
-        <v>58646800</v>
+        <v>31543600</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="B204" t="n">
-        <v>45.47278594970703</v>
+        <v>46.73382568359375</v>
       </c>
       <c r="C204" t="n">
-        <v>46.64621376126109</v>
+        <v>47.24522321125404</v>
       </c>
       <c r="D204" t="n">
-        <v>45.31762197214121</v>
+        <v>46.67481697792989</v>
       </c>
       <c r="E204" t="n">
-        <v>46.50074961320622</v>
+        <v>46.86167600340548</v>
       </c>
       <c r="F204" t="n">
-        <v>61852100</v>
+        <v>29389700</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>46128</v>
+        <v>46141</v>
       </c>
       <c r="B205" t="n">
-        <v>47.1117057800293</v>
+        <v>48.15000152587891</v>
       </c>
       <c r="C205" t="n">
-        <v>47.20868187129476</v>
+        <v>48.48437669279139</v>
       </c>
       <c r="D205" t="n">
-        <v>45.34671058391167</v>
+        <v>47.20588473162716</v>
       </c>
       <c r="E205" t="n">
-        <v>45.86069422594074</v>
+        <v>47.30422882418338</v>
       </c>
       <c r="F205" t="n">
-        <v>54484300</v>
+        <v>47685000</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>46129</v>
+        <v>46142</v>
       </c>
       <c r="B206" t="n">
-        <v>44.82303619384766</v>
+        <v>48.26801681518555</v>
       </c>
       <c r="C206" t="n">
-        <v>45.14306026655282</v>
+        <v>48.56305283146008</v>
       </c>
       <c r="D206" t="n">
-        <v>43.51383671623324</v>
+        <v>47.49108576277963</v>
       </c>
       <c r="E206" t="n">
-        <v>45.09457221910063</v>
+        <v>48.00248327506252</v>
       </c>
       <c r="F206" t="n">
-        <v>105186900</v>
+        <v>36666100</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="B207" t="n">
-        <v>45.59885787963867</v>
+        <v>48.52371597290039</v>
       </c>
       <c r="C207" t="n">
-        <v>46.0449538531271</v>
+        <v>49.02527684894824</v>
       </c>
       <c r="D207" t="n">
-        <v>45.10427015735281</v>
+        <v>48.11066252946099</v>
       </c>
       <c r="E207" t="n">
-        <v>45.81220973626403</v>
+        <v>48.46470726624143</v>
       </c>
       <c r="F207" t="n">
-        <v>41904500</v>
+        <v>41319600</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="B208" t="n">
-        <v>46.22920608520508</v>
+        <v>47.85496520996094</v>
       </c>
       <c r="C208" t="n">
-        <v>46.52983788556254</v>
+        <v>48.21884285214325</v>
       </c>
       <c r="D208" t="n">
-        <v>45.82190206478599</v>
+        <v>47.53042670520012</v>
       </c>
       <c r="E208" t="n">
-        <v>46.20011399786107</v>
+        <v>48.07132671419257</v>
       </c>
       <c r="F208" t="n">
-        <v>51063000</v>
+        <v>28066500</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>46135</v>
+        <v>46148</v>
       </c>
       <c r="B209" t="n">
-        <v>46.97968673706055</v>
+        <v>46.48796081542969</v>
       </c>
       <c r="C209" t="n">
-        <v>47.28455940328853</v>
+        <v>46.70432231380818</v>
       </c>
       <c r="D209" t="n">
-        <v>46.12408119195152</v>
+        <v>45.81921050370212</v>
       </c>
       <c r="E209" t="n">
-        <v>46.57646998577134</v>
+        <v>45.93722416118741</v>
       </c>
       <c r="F209" t="n">
-        <v>38666800</v>
+        <v>62009100</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>46136</v>
+        <v>46149</v>
       </c>
       <c r="B210" t="n">
-        <v>46.37977981567383</v>
+        <v>45.4553337097168</v>
       </c>
       <c r="C210" t="n">
-        <v>46.73382453780353</v>
+        <v>45.87822005439067</v>
       </c>
       <c r="D210" t="n">
-        <v>45.68152703124387</v>
+        <v>44.45220822362435</v>
       </c>
       <c r="E210" t="n">
-        <v>46.71415496973115</v>
+        <v>45.63235607500291</v>
       </c>
       <c r="F210" t="n">
-        <v>34880200</v>
+        <v>71214500</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>46139</v>
+        <v>46150</v>
       </c>
       <c r="B211" t="n">
-        <v>46.5863037109375</v>
+        <v>44.9144287109375</v>
       </c>
       <c r="C211" t="n">
-        <v>47.37306765998913</v>
+        <v>45.77987094487844</v>
       </c>
       <c r="D211" t="n">
-        <v>46.38961178577799</v>
+        <v>44.9144287109375</v>
       </c>
       <c r="E211" t="n">
-        <v>46.43878758075769</v>
+        <v>45.62251815248795</v>
       </c>
       <c r="F211" t="n">
-        <v>31543600</v>
+        <v>32914200</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="B212" t="n">
-        <v>46.73382568359375</v>
+        <v>45.66185760498047</v>
       </c>
       <c r="C212" t="n">
-        <v>47.24522321125404</v>
+        <v>45.74053212592779</v>
       </c>
       <c r="D212" t="n">
-        <v>46.67481697792989</v>
+        <v>44.89476320570814</v>
       </c>
       <c r="E212" t="n">
-        <v>46.86167600340548</v>
+        <v>45.44549610709893</v>
       </c>
       <c r="F212" t="n">
-        <v>29389700</v>
+        <v>50622200</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>46141</v>
+        <v>46154</v>
       </c>
       <c r="B213" t="n">
-        <v>48.15000152587891</v>
+        <v>44.92426681518555</v>
       </c>
       <c r="C213" t="n">
-        <v>48.48437669279139</v>
+        <v>45.48483639057489</v>
       </c>
       <c r="D213" t="n">
-        <v>47.20588473162716</v>
+        <v>44.64890035754492</v>
       </c>
       <c r="E213" t="n">
-        <v>47.30422882418338</v>
+        <v>45.48483639057489</v>
       </c>
       <c r="F213" t="n">
-        <v>47685000</v>
+        <v>81072700</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>46142</v>
+        <v>46155</v>
       </c>
       <c r="B214" t="n">
-        <v>48.26801681518555</v>
+        <v>43.8326301574707</v>
       </c>
       <c r="C214" t="n">
-        <v>48.56305283146008</v>
+        <v>45.07178672047662</v>
       </c>
       <c r="D214" t="n">
-        <v>47.49108576277963</v>
+        <v>43.62610531416526</v>
       </c>
       <c r="E214" t="n">
-        <v>48.00248327506252</v>
+        <v>45.01277801456651</v>
       </c>
       <c r="F214" t="n">
-        <v>36666100</v>
+        <v>57251900</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>46146</v>
+        <v>46156</v>
       </c>
       <c r="B215" t="n">
-        <v>48.52371597290039</v>
+        <v>44.25551605224609</v>
       </c>
       <c r="C215" t="n">
-        <v>49.02527684894824</v>
+        <v>44.61939368934254</v>
       </c>
       <c r="D215" t="n">
-        <v>48.11066252946099</v>
+        <v>43.64577443708161</v>
       </c>
       <c r="E215" t="n">
-        <v>48.46470726624143</v>
+        <v>43.72444895923837</v>
       </c>
       <c r="F215" t="n">
-        <v>41319600</v>
+        <v>47760000</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="B216" t="n">
-        <v>47.85496520996094</v>
+        <v>44.71773910522461</v>
       </c>
       <c r="C216" t="n">
-        <v>48.21884285214325</v>
+        <v>44.78658071522153</v>
       </c>
       <c r="D216" t="n">
-        <v>47.53042670520012</v>
+        <v>44.23584408365985</v>
       </c>
       <c r="E216" t="n">
-        <v>48.07132671419257</v>
+        <v>44.63906083575021</v>
       </c>
       <c r="F216" t="n">
-        <v>28066500</v>
+        <v>59380500</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="B217" t="n">
-        <v>46.48796081542969</v>
+        <v>45.67169189453125</v>
       </c>
       <c r="C217" t="n">
-        <v>46.70432231380818</v>
+        <v>45.69136146325959</v>
       </c>
       <c r="D217" t="n">
-        <v>45.81921050370212</v>
+        <v>43.73428626962283</v>
       </c>
       <c r="E217" t="n">
-        <v>45.93722416118741</v>
+        <v>44.35386080242564</v>
       </c>
       <c r="F217" t="n">
-        <v>62009100</v>
+        <v>57388200</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="B218" t="n">
-        <v>45.4553337097168</v>
+        <v>45.32748413085938</v>
       </c>
       <c r="C218" t="n">
-        <v>45.87822005439067</v>
+        <v>45.53400897653992</v>
       </c>
       <c r="D218" t="n">
-        <v>44.45220822362435</v>
+        <v>44.83575616404666</v>
       </c>
       <c r="E218" t="n">
-        <v>45.63235607500291</v>
+        <v>45.2291400381315</v>
       </c>
       <c r="F218" t="n">
-        <v>71214500</v>
+        <v>40943000</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="B219" t="n">
-        <v>44.9144287109375</v>
+        <v>43.86213302612305</v>
       </c>
       <c r="C219" t="n">
-        <v>45.77987094487844</v>
+        <v>45.64218961197297</v>
       </c>
       <c r="D219" t="n">
-        <v>44.9144287109375</v>
+        <v>43.80312807127291</v>
       </c>
       <c r="E219" t="n">
-        <v>45.62251815248795</v>
+        <v>45.01277841632718</v>
       </c>
       <c r="F219" t="n">
-        <v>32914200</v>
+        <v>52780200</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>46153</v>
+        <v>46163</v>
       </c>
       <c r="B220" t="n">
-        <v>45.66185760498047</v>
+        <v>44.20634460449219</v>
       </c>
       <c r="C220" t="n">
-        <v>45.74053212592779</v>
+        <v>44.89476450270546</v>
       </c>
       <c r="D220" t="n">
-        <v>44.89476320570814</v>
+        <v>43.76378868767033</v>
       </c>
       <c r="E220" t="n">
-        <v>45.44549610709893</v>
+        <v>44.35386074237505</v>
       </c>
       <c r="F220" t="n">
-        <v>50622200</v>
+        <v>57725900</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>46154</v>
+        <v>46164</v>
       </c>
       <c r="B221" t="n">
-        <v>44.92426681518555</v>
+        <v>43.74411773681641</v>
       </c>
       <c r="C221" t="n">
-        <v>45.48483639057489</v>
+        <v>44.00965127851964</v>
       </c>
       <c r="D221" t="n">
-        <v>44.64890035754492</v>
+        <v>43.14420904092241</v>
       </c>
       <c r="E221" t="n">
-        <v>45.48483639057489</v>
+        <v>43.99981837027278</v>
       </c>
       <c r="F221" t="n">
-        <v>81072700</v>
+        <v>39634300</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>46155</v>
+        <v>46167</v>
       </c>
       <c r="B222" t="n">
-        <v>43.8326301574707</v>
+        <v>42.68198776245117</v>
       </c>
       <c r="C222" t="n">
-        <v>45.07178672047662</v>
+        <v>43.0950374416427</v>
       </c>
       <c r="D222" t="n">
-        <v>43.62610531416526</v>
+        <v>42.25910142332469</v>
       </c>
       <c r="E222" t="n">
-        <v>45.01277801456651</v>
+        <v>42.77049894393315</v>
       </c>
       <c r="F222" t="n">
-        <v>57251900</v>
+        <v>26720900</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>46156</v>
+        <v>46168</v>
       </c>
       <c r="B223" t="n">
-        <v>44.25551605224609</v>
+        <v>42.72132110595703</v>
       </c>
       <c r="C223" t="n">
-        <v>44.61939368934254</v>
+        <v>43.07536581496661</v>
       </c>
       <c r="D223" t="n">
-        <v>43.64577443708161</v>
+        <v>42.44595466632131</v>
       </c>
       <c r="E223" t="n">
-        <v>43.72444895923837</v>
+        <v>42.64264658816955</v>
       </c>
       <c r="F223" t="n">
-        <v>47760000</v>
+        <v>36040500</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>46157</v>
+        <v>46169</v>
       </c>
       <c r="B224" t="n">
-        <v>44.71773910522461</v>
+        <v>42.11157989501953</v>
       </c>
       <c r="C224" t="n">
-        <v>44.78658071522153</v>
+        <v>42.4754575151079</v>
       </c>
       <c r="D224" t="n">
-        <v>44.23584408365985</v>
+        <v>41.45266626535718</v>
       </c>
       <c r="E224" t="n">
-        <v>44.63906083575021</v>
+        <v>41.55101035135304</v>
       </c>
       <c r="F224" t="n">
-        <v>59380500</v>
+        <v>53745400</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="n">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="B225" t="n">
-        <v>45.67169189453125</v>
+        <v>41.80670928955078</v>
       </c>
       <c r="C225" t="n">
-        <v>45.69136146325959</v>
+        <v>42.46562670332492</v>
       </c>
       <c r="D225" t="n">
-        <v>43.73428626962283</v>
+        <v>41.55101240238803</v>
       </c>
       <c r="E225" t="n">
-        <v>44.35386080242564</v>
+        <v>42.3869484293754</v>
       </c>
       <c r="F225" t="n">
-        <v>57388200</v>
+        <v>37534800</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="n">
-        <v>46161</v>
+        <v>46171</v>
       </c>
       <c r="B226" t="n">
-        <v>45.32748413085938</v>
+        <v>41.30514907836914</v>
       </c>
       <c r="C226" t="n">
-        <v>45.53400897653992</v>
+        <v>41.64935715338756</v>
       </c>
       <c r="D226" t="n">
-        <v>44.83575616404666</v>
+        <v>41.12812671076348</v>
       </c>
       <c r="E226" t="n">
-        <v>45.2291400381315</v>
+        <v>41.50184101477394</v>
       </c>
       <c r="F226" t="n">
-        <v>40943000</v>
+        <v>73281800</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="n">
-        <v>46162</v>
+        <v>46174</v>
       </c>
       <c r="B227" t="n">
-        <v>43.86213302612305</v>
+        <v>41.66902542114258</v>
       </c>
       <c r="C227" t="n">
-        <v>45.64218961197297</v>
+        <v>42.3082732566021</v>
       </c>
       <c r="D227" t="n">
-        <v>43.80312807127291</v>
+        <v>41.26580865231648</v>
       </c>
       <c r="E227" t="n">
-        <v>45.01277841632718</v>
+        <v>41.69853164921334</v>
       </c>
       <c r="F227" t="n">
-        <v>52780200</v>
+        <v>73925300</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="n">
-        <v>46163</v>
+        <v>46175</v>
       </c>
       <c r="B228" t="n">
-        <v>44.20634460449219</v>
+        <v>41.56999969482422</v>
       </c>
       <c r="C228" t="n">
-        <v>44.89476450270546</v>
+        <v>41.97999954223633</v>
       </c>
       <c r="D228" t="n">
-        <v>43.76378868767033</v>
+        <v>41.43999862670898</v>
       </c>
       <c r="E228" t="n">
-        <v>44.35386074237505</v>
+        <v>41.90000152587891</v>
       </c>
       <c r="F228" t="n">
-        <v>57725900</v>
+        <v>27318300</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="n">
-        <v>46164</v>
+        <v>46176</v>
       </c>
       <c r="B229" t="n">
-        <v>43.74411773681641</v>
+        <v>41.25</v>
       </c>
       <c r="C229" t="n">
-        <v>44.00965127851964</v>
+        <v>41.86999893188477</v>
       </c>
       <c r="D229" t="n">
-        <v>43.14420904092241</v>
+        <v>41.25</v>
       </c>
       <c r="E229" t="n">
-        <v>43.99981837027278</v>
+        <v>41.65000152587891</v>
       </c>
       <c r="F229" t="n">
-        <v>39634300</v>
+        <v>42895100</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="n">
-        <v>46167</v>
+        <v>46178</v>
       </c>
       <c r="B230" t="n">
-        <v>42.68198776245117</v>
+        <v>40.88999938964844</v>
       </c>
       <c r="C230" t="n">
-        <v>43.0950374416427</v>
+        <v>41.43000030517578</v>
       </c>
       <c r="D230" t="n">
-        <v>42.25910142332469</v>
+        <v>40.65000152587891</v>
       </c>
       <c r="E230" t="n">
-        <v>42.77049894393315</v>
+        <v>41.02999877929688</v>
       </c>
       <c r="F230" t="n">
-        <v>26720900</v>
+        <v>34730900</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="n">
-        <v>46168</v>
+        <v>46181</v>
       </c>
       <c r="B231" t="n">
-        <v>42.72132110595703</v>
+        <v>41.22000122070312</v>
       </c>
       <c r="C231" t="n">
-        <v>43.07536581496661</v>
+        <v>41.31999969482422</v>
       </c>
       <c r="D231" t="n">
-        <v>42.44595466632131</v>
+        <v>40.83000183105469</v>
       </c>
       <c r="E231" t="n">
-        <v>42.64264658816955</v>
+        <v>41.20000076293945</v>
       </c>
       <c r="F231" t="n">
-        <v>36040500</v>
+        <v>34043600</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="n">
-        <v>46169</v>
+        <v>46182</v>
       </c>
       <c r="B232" t="n">
-        <v>42.11157989501953</v>
+        <v>41.16999816894531</v>
       </c>
       <c r="C232" t="n">
-        <v>42.4754575151079</v>
+        <v>41.36999893188477</v>
       </c>
       <c r="D232" t="n">
-        <v>41.45266626535718</v>
+        <v>40.70000076293945</v>
       </c>
       <c r="E232" t="n">
-        <v>41.55101035135304</v>
+        <v>40.88000106811523</v>
       </c>
       <c r="F232" t="n">
-        <v>53745400</v>
+        <v>56680400</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="n">
-        <v>46170</v>
+        <v>46183</v>
       </c>
       <c r="B233" t="n">
-        <v>41.80670928955078</v>
+        <v>41.65000152587891</v>
       </c>
       <c r="C233" t="n">
-        <v>42.46562670332492</v>
+        <v>42.04000091552734</v>
       </c>
       <c r="D233" t="n">
-        <v>41.55101240238803</v>
+        <v>41.0099983215332</v>
       </c>
       <c r="E233" t="n">
-        <v>42.3869484293754</v>
+        <v>41.20999908447266</v>
       </c>
       <c r="F233" t="n">
-        <v>37534800</v>
+        <v>44953200</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="n">
-        <v>46171</v>
+        <v>46184</v>
       </c>
       <c r="B234" t="n">
-        <v>41.30514907836914</v>
+        <v>41.7599983215332</v>
       </c>
       <c r="C234" t="n">
-        <v>41.64935715338756</v>
+        <v>42.15000152587891</v>
       </c>
       <c r="D234" t="n">
-        <v>41.12812671076348</v>
+        <v>41.15999984741211</v>
       </c>
       <c r="E234" t="n">
-        <v>41.50184101477394</v>
+        <v>41.65000152587891</v>
       </c>
       <c r="F234" t="n">
-        <v>73281800</v>
+        <v>52321500</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="n">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="B235" t="n">
-        <v>41.66902542114258</v>
+        <v>41.18000030517578</v>
       </c>
       <c r="C235" t="n">
-        <v>42.3082732566021</v>
+        <v>41.52999877929688</v>
       </c>
       <c r="D235" t="n">
-        <v>41.26580865231648</v>
+        <v>40.81999969482422</v>
       </c>
       <c r="E235" t="n">
-        <v>41.69853164921334</v>
+        <v>41.06000137329102</v>
       </c>
       <c r="F235" t="n">
-        <v>73925300</v>
+        <v>34082200</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="n">
-        <v>46175</v>
+        <v>46188</v>
       </c>
       <c r="B236" t="n">
-        <v>41.56999969482422</v>
+        <v>39.06000137329102</v>
       </c>
       <c r="C236" t="n">
-        <v>41.97999954223633</v>
+        <v>39.91999816894531</v>
       </c>
       <c r="D236" t="n">
-        <v>41.43999862670898</v>
+        <v>39.06000137329102</v>
       </c>
       <c r="E236" t="n">
-        <v>41.90000152587891</v>
+        <v>39.84000015258789</v>
       </c>
       <c r="F236" t="n">
-        <v>27318300</v>
+        <v>54174000</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="n">
-        <v>46176</v>
+        <v>46189</v>
       </c>
       <c r="B237" t="n">
-        <v>41.25</v>
+        <v>38.54000091552734</v>
       </c>
       <c r="C237" t="n">
-        <v>41.86999893188477</v>
+        <v>38.77999877929688</v>
       </c>
       <c r="D237" t="n">
-        <v>41.25</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="E237" t="n">
-        <v>41.65000152587891</v>
+        <v>38.45000076293945</v>
       </c>
       <c r="F237" t="n">
-        <v>42895100</v>
+        <v>36250100</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="n">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="B238" t="n">
-        <v>40.88999938964844</v>
+        <v>38.56999969482422</v>
       </c>
       <c r="C238" t="n">
-        <v>41.43000030517578</v>
+        <v>38.86000061035156</v>
       </c>
       <c r="D238" t="n">
-        <v>40.65000152587891</v>
+        <v>38.27000045776367</v>
       </c>
       <c r="E238" t="n">
-        <v>41.02999877929688</v>
+        <v>38.70999908447266</v>
       </c>
       <c r="F238" t="n">
-        <v>34730900</v>
+        <v>66882000</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="n">
-        <v>46181</v>
+        <v>46191</v>
       </c>
       <c r="B239" t="n">
-        <v>41.22000122070312</v>
+        <v>38.84999847412109</v>
       </c>
       <c r="C239" t="n">
-        <v>41.31999969482422</v>
+        <v>39.09000015258789</v>
       </c>
       <c r="D239" t="n">
-        <v>40.83000183105469</v>
+        <v>37.40999984741211</v>
       </c>
       <c r="E239" t="n">
-        <v>41.20000076293945</v>
+        <v>38.29999923706055</v>
       </c>
       <c r="F239" t="n">
-        <v>34043600</v>
+        <v>53332600</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="n">
-        <v>46182</v>
+        <v>46192</v>
       </c>
       <c r="B240" t="n">
-        <v>41.16999816894531</v>
+        <v>38.79999923706055</v>
       </c>
       <c r="C240" t="n">
-        <v>41.36999893188477</v>
+        <v>39.11000061035156</v>
       </c>
       <c r="D240" t="n">
-        <v>40.70000076293945</v>
+        <v>38.61999893188477</v>
       </c>
       <c r="E240" t="n">
-        <v>40.88000106811523</v>
+        <v>38.86000061035156</v>
       </c>
       <c r="F240" t="n">
-        <v>56680400</v>
+        <v>44775800</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="n">
-        <v>46183</v>
+        <v>46195</v>
       </c>
       <c r="B241" t="n">
-        <v>41.65000152587891</v>
+        <v>39.16999816894531</v>
       </c>
       <c r="C241" t="n">
-        <v>42.04000091552734</v>
+        <v>39.20999908447266</v>
       </c>
       <c r="D241" t="n">
-        <v>41.0099983215332</v>
+        <v>38.47999954223633</v>
       </c>
       <c r="E241" t="n">
-        <v>41.20999908447266</v>
+        <v>38.75</v>
       </c>
       <c r="F241" t="n">
-        <v>44953200</v>
+        <v>35488200</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="n">
-        <v>46184</v>
+        <v>46196</v>
       </c>
       <c r="B242" t="n">
-        <v>41.7599983215332</v>
+        <v>39.33000183105469</v>
       </c>
       <c r="C242" t="n">
-        <v>42.15000152587891</v>
+        <v>39.56999969482422</v>
       </c>
       <c r="D242" t="n">
-        <v>41.15999984741211</v>
+        <v>38.84000015258789</v>
       </c>
       <c r="E242" t="n">
-        <v>41.65000152587891</v>
+        <v>38.95999908447266</v>
       </c>
       <c r="F242" t="n">
-        <v>52321500</v>
+        <v>27398600</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="n">
-        <v>46185</v>
+        <v>46197</v>
       </c>
       <c r="B243" t="n">
-        <v>41.18000030517578</v>
+        <v>38.29000091552734</v>
       </c>
       <c r="C243" t="n">
-        <v>41.52999877929688</v>
+        <v>38.97999954223633</v>
       </c>
       <c r="D243" t="n">
-        <v>40.81999969482422</v>
+        <v>38.13000106811523</v>
       </c>
       <c r="E243" t="n">
-        <v>41.06000137329102</v>
+        <v>38.90000152587891</v>
       </c>
       <c r="F243" t="n">
-        <v>34082200</v>
+        <v>59191400</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="n">
-        <v>46188</v>
+        <v>46198</v>
       </c>
       <c r="B244" t="n">
-        <v>39.06000137329102</v>
+        <v>38.45000076293945</v>
       </c>
       <c r="C244" t="n">
-        <v>39.91999816894531</v>
+        <v>38.66999816894531</v>
       </c>
       <c r="D244" t="n">
-        <v>39.06000137329102</v>
+        <v>37.91999816894531</v>
       </c>
       <c r="E244" t="n">
-        <v>39.84000015258789</v>
+        <v>38.11999893188477</v>
       </c>
       <c r="F244" t="n">
-        <v>54174000</v>
+        <v>25152300</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="n">
-        <v>46189</v>
+        <v>46199</v>
       </c>
       <c r="B245" t="n">
-        <v>38.54000091552734</v>
+        <v>38.06000137329102</v>
       </c>
       <c r="C245" t="n">
-        <v>38.77999877929688</v>
+        <v>38.25</v>
       </c>
       <c r="D245" t="n">
-        <v>38.20000076293945</v>
+        <v>37.93000030517578</v>
       </c>
       <c r="E245" t="n">
-        <v>38.45000076293945</v>
+        <v>38.06999969482422</v>
       </c>
       <c r="F245" t="n">
-        <v>36250100</v>
+        <v>23383000</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="n">
-        <v>46190</v>
+        <v>46202</v>
       </c>
       <c r="B246" t="n">
-        <v>38.56999969482422</v>
+        <v>38.13999938964844</v>
       </c>
       <c r="C246" t="n">
-        <v>38.86000061035156</v>
+        <v>38.36999893188477</v>
       </c>
       <c r="D246" t="n">
-        <v>38.27000045776367</v>
+        <v>37.91999816894531</v>
       </c>
       <c r="E246" t="n">
-        <v>38.70999908447266</v>
+        <v>38.20000076293945</v>
       </c>
       <c r="F246" t="n">
-        <v>66882000</v>
+        <v>14924800</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="n">
-        <v>46191</v>
+        <v>46203</v>
       </c>
       <c r="B247" t="n">
-        <v>38.84999847412109</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="C247" t="n">
-        <v>39.09000015258789</v>
+        <v>38.18000030517578</v>
       </c>
       <c r="D247" t="n">
-        <v>37.40999984741211</v>
+        <v>37.7400016784668</v>
       </c>
       <c r="E247" t="n">
-        <v>38.29999923706055</v>
+        <v>38.16999816894531</v>
       </c>
       <c r="F247" t="n">
-        <v>53332600</v>
+        <v>31974300</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="n">
-        <v>46192</v>
+        <v>46204</v>
       </c>
       <c r="B248" t="n">
-        <v>38.79999923706055</v>
+        <v>37.83000183105469</v>
       </c>
       <c r="C248" t="n">
-        <v>39.11000061035156</v>
+        <v>37.84000015258789</v>
       </c>
       <c r="D248" t="n">
-        <v>38.61999893188477</v>
+        <v>37.40000152587891</v>
       </c>
       <c r="E248" t="n">
-        <v>38.86000061035156</v>
+        <v>37.5</v>
       </c>
       <c r="F248" t="n">
-        <v>44775800</v>
+        <v>21094300</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="n">
-        <v>46195</v>
+        <v>46205</v>
       </c>
       <c r="B249" t="n">
-        <v>39.16999816894531</v>
+        <v>37.95999908447266</v>
       </c>
       <c r="C249" t="n">
-        <v>39.20999908447266</v>
+        <v>38.45999908447266</v>
       </c>
       <c r="D249" t="n">
-        <v>38.47999954223633</v>
+        <v>37.65000152587891</v>
       </c>
       <c r="E249" t="n">
-        <v>38.75</v>
+        <v>37.88999938964844</v>
       </c>
       <c r="F249" t="n">
-        <v>35488200</v>
+        <v>21888800</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="n">
-        <v>46196</v>
+        <v>46206</v>
       </c>
       <c r="B250" t="n">
-        <v>39.33000183105469</v>
+        <v>38.25</v>
       </c>
       <c r="C250" t="n">
-        <v>39.56999969482422</v>
+        <v>38.25</v>
       </c>
       <c r="D250" t="n">
-        <v>38.84000015258789</v>
+        <v>37.86000061035156</v>
       </c>
       <c r="E250" t="n">
-        <v>38.95999908447266</v>
+        <v>38.06999969482422</v>
       </c>
       <c r="F250" t="n">
-        <v>27398600</v>
+        <v>10369500</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="n">
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="B251" t="n">
-        <v>38.29000091552734</v>
+        <v>37.77000045776367</v>
       </c>
       <c r="C251" t="n">
-        <v>38.97999954223633</v>
+        <v>38.02000045776367</v>
       </c>
       <c r="D251" t="n">
-        <v>38.13000106811523</v>
+        <v>37.61000061035156</v>
       </c>
       <c r="E251" t="n">
-        <v>38.90000152587891</v>
+        <v>37.95000076293945</v>
       </c>
       <c r="F251" t="n">
-        <v>59191400</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="B252" t="n">
-        <v>38.43000030517578</v>
-      </c>
-      <c r="C252" t="n">
-        <v>38.66999816894531</v>
-      </c>
-      <c r="D252" t="n">
-        <v>37.91999816894531</v>
-      </c>
-      <c r="E252" t="n">
-        <v>38.11999893188477</v>
-      </c>
-      <c r="F252" t="n">
-        <v>21502600</v>
+        <v>20770300</v>
       </c>
     </row>
   </sheetData>
